--- a/Holiday_Calendar_2026_2027.xlsx
+++ b/Holiday_Calendar_2026_2027.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Hong Kong'!$A$2:$H$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Singapore'!$A$2:$H$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'China'!$A$2:$H$76</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Squash Junior Events'!$A$2:$L$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Squash Junior Events'!$A$2:$L$72</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -152,7 +152,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -199,6 +199,17 @@
       <right style="thin">
         <color rgb="00BFBFBF"/>
       </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="00BFBFBF"/>
       </top>
@@ -20677,7 +20688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22042,12 +22053,12 @@
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>12 Aug 2026</t>
+          <t>5 Aug 2026</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>15 Aug 2026</t>
+          <t>9 Aug 2026</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
@@ -22057,7 +22068,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>19th Korea Junior Open 2026 ★</t>
+          <t>Egyptian Junior Open 2026</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -22073,339 +22084,339 @@
       <c r="G25" s="7" t="inlineStr"/>
       <c r="H25" s="8" t="inlineStr">
         <is>
+          <t>ESF / Egyptian Squash Federation</t>
+        </is>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
+        <is>
+          <t>Cairo, Egypt</t>
+        </is>
+      </c>
+      <c r="J25" s="8" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Gold. Source: europeansquash.com/event/egyptian-junior-open-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>7 Aug 2026</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>9 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Finnish Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>ESF / Finnish Squash Federation</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>Talihalli, Helsinki, Finland</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/finnish-junior-open-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>12 Aug 2026</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>15 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>19th Korea Junior Open 2026 ★</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
           <t>Korea Squash / ASF</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="J25" s="8" t="inlineStr">
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="K25" s="8" t="inlineStr">
+      <c r="K27" s="8" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
+      <c r="L27" s="8" t="inlineStr">
         <is>
           <t>AJSS Gold. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>14 Aug 2026</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>16 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Turkish Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E28" s="26" t="inlineStr">
+        <is>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="F28" s="25" t="inlineStr">
+        <is>
+          <t>~ Estimated</t>
+        </is>
+      </c>
+      <c r="G28" s="25" t="inlineStr"/>
+      <c r="H28" s="26" t="inlineStr">
+        <is>
+          <t>ESF / Turkish Squash Federation</t>
+        </is>
+      </c>
+      <c r="I28" s="26" t="inlineStr">
+        <is>
+          <t>Istanbul, Turkey</t>
+        </is>
+      </c>
+      <c r="J28" s="26" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="K28" s="26" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/turkish-junior-open-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>17 Aug 2026</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>22 Aug 2026</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="D26" s="8" t="inlineStr">
+      <c r="D29" s="8" t="inlineStr">
         <is>
           <t>Southern Slam 2026 ★</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr">
         <is>
           <t>India Squash / ASF</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>Chennai, India</t>
         </is>
       </c>
-      <c r="J26" s="8" t="inlineStr">
+      <c r="J29" s="8" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="K26" s="8" t="inlineStr">
+      <c r="K29" s="8" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L26" s="8" t="inlineStr">
+      <c r="L29" s="8" t="inlineStr">
         <is>
           <t>AJSS Gold. Entry deadline: 15 Jul 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>19 Aug 2026</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>23 Aug 2026</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C30" s="11" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>37th Japan Junior Open 2026 ★</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E30" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F30" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr"/>
-      <c r="H27" s="12" t="inlineStr">
+      <c r="G30" s="11" t="inlineStr"/>
+      <c r="H30" s="12" t="inlineStr">
         <is>
           <t>Japan Squash / ASF</t>
         </is>
       </c>
-      <c r="I27" s="12" t="inlineStr">
+      <c r="I30" s="12" t="inlineStr">
         <is>
           <t>Yokohama &amp; Ebina, Japan</t>
         </is>
       </c>
-      <c r="J27" s="12" t="inlineStr">
+      <c r="J30" s="12" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="K27" s="12" t="inlineStr">
+      <c r="K30" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L27" s="12" t="inlineStr">
+      <c r="L30" s="12" t="inlineStr">
         <is>
           <t>AJSS Silver. Entry deadline: 25 Jun 2026 12:00 JST. Source: asiansquash.org/eventpage/ajss-event</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>25 Aug 2026</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>27 Aug 2026</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>Qatar Junior Open 2026 ★</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="inlineStr"/>
-      <c r="H28" s="12" t="inlineStr">
-        <is>
-          <t>Qatar Squash / ASF</t>
-        </is>
-      </c>
-      <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>Doha, Qatar</t>
-        </is>
-      </c>
-      <c r="J28" s="12" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
-      </c>
-      <c r="K28" s="12" t="inlineStr">
-        <is>
-          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
-        </is>
-      </c>
-      <c r="L28" s="12" t="inlineStr">
-        <is>
-          <t>AJSS Silver. Entry deadline: 6 Aug 2026. Source: asiansquash.org/eventpage/ajss-event</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>25 Aug 2026</t>
-        </is>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>29 Aug 2026</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>1st Chinese Taipei Junior Squash Open 2026 ★</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="F29" s="11" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G29" s="11" t="inlineStr"/>
-      <c r="H29" s="12" t="inlineStr">
-        <is>
-          <t>Chinese Taipei Squash / ASF</t>
-        </is>
-      </c>
-      <c r="I29" s="12" t="inlineStr">
-        <is>
-          <t>Taipei, Chinese Taipei</t>
-        </is>
-      </c>
-      <c r="J29" s="12" t="inlineStr">
-        <is>
-          <t>Chinese Taipei</t>
-        </is>
-      </c>
-      <c r="K29" s="12" t="inlineStr">
-        <is>
-          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
-        </is>
-      </c>
-      <c r="L29" s="12" t="inlineStr">
-        <is>
-          <t>AJSS Silver — inaugural edition. Entry deadline: 5 Aug 2026. Source: asiansquash.org/eventpage/ajss-event</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>26 Aug 2026</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>30 Aug 2026</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>Wed</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>Macau Junior Squash Open 2026 ★</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>Macau Squash / ASF</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>Macau, China</t>
-        </is>
-      </c>
-      <c r="J30" s="8" t="inlineStr">
-        <is>
-          <t>Macau</t>
-        </is>
-      </c>
-      <c r="K30" s="8" t="inlineStr">
-        <is>
-          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
-        </is>
-      </c>
-      <c r="L30" s="8" t="inlineStr">
-        <is>
-          <t>AJSS Gold. Entry deadline: 29 Jul 2026 12:00 Macau Time. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>4 Sep 2026</t>
+          <t>25 Aug 2026</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>6 Sep 2026</t>
+          <t>27 Aug 2026</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Welsh Junior Open 2026</t>
+          <t>Qatar Junior Open 2026 ★</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
@@ -22421,459 +22432,455 @@
       <c r="G31" s="11" t="inlineStr"/>
       <c r="H31" s="12" t="inlineStr">
         <is>
+          <t>Qatar Squash / ASF</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>Doha, Qatar</t>
+        </is>
+      </c>
+      <c r="J31" s="12" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="K31" s="12" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>AJSS Silver. Entry deadline: 6 Aug 2026. Source: asiansquash.org/eventpage/ajss-event</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>25 Aug 2026</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>29 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>1st Chinese Taipei Junior Squash Open 2026 ★</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr"/>
+      <c r="H32" s="12" t="inlineStr">
+        <is>
+          <t>Chinese Taipei Squash / ASF</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>Taipei, Chinese Taipei</t>
+        </is>
+      </c>
+      <c r="J32" s="12" t="inlineStr">
+        <is>
+          <t>Chinese Taipei</t>
+        </is>
+      </c>
+      <c r="K32" s="12" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L32" s="12" t="inlineStr">
+        <is>
+          <t>AJSS Silver — inaugural edition. Entry deadline: 5 Aug 2026. Source: asiansquash.org/eventpage/ajss-event</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>26 Aug 2026</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>30 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Macau Junior Squash Open 2026 ★</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>Macau Squash / ASF</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t>Macau, China</t>
+        </is>
+      </c>
+      <c r="J33" s="8" t="inlineStr">
+        <is>
+          <t>Macau</t>
+        </is>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>AJSS Gold. Entry deadline: 29 Jul 2026 12:00 Macau Time. Source: asiansquash.org/eventpage/ajss-event</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>4 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>6 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Welsh Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr"/>
+      <c r="H34" s="12" t="inlineStr">
+        <is>
           <t>ESF / Squash Wales</t>
         </is>
       </c>
-      <c r="I31" s="12" t="inlineStr">
+      <c r="I34" s="12" t="inlineStr">
         <is>
           <t>Sport Wales National Centre, Cardiff</t>
         </is>
       </c>
-      <c r="J31" s="12" t="inlineStr">
+      <c r="J34" s="12" t="inlineStr">
         <is>
           <t>Wales</t>
         </is>
       </c>
-      <c r="K31" s="12" t="inlineStr">
+      <c r="K34" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L31" s="12" t="inlineStr">
+      <c r="L34" s="12" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Silver. Entry deadline was 14 Aug 2026. Source: europeansquash.com / scottishsquash.org</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>18 Sep 2026</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>20 Sep 2026</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>Slovak Junior Open 2026</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>ESF / Slovak Squash Federation</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>Bratislava, Slovakia</t>
         </is>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr">
         <is>
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="K35" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L32" s="4" t="inlineStr">
+      <c r="L35" s="4" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/slovak-junior-open-2026</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>19 Sep 2026</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>24 Sep 2026</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D33" s="10" t="inlineStr">
+      <c r="D36" s="10" t="inlineStr">
         <is>
           <t>Indian Junior Open 2026 ★</t>
         </is>
       </c>
-      <c r="E33" s="10" t="inlineStr">
+      <c r="E36" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F33" s="9" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr"/>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="G36" s="9" t="inlineStr"/>
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>Squash Rackets Federation of India / ASF</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Kolkata, India</t>
         </is>
       </c>
-      <c r="J33" s="10" t="inlineStr">
+      <c r="J36" s="10" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="K33" s="10" t="inlineStr">
+      <c r="K36" s="10" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L33" s="10" t="inlineStr">
+      <c r="L36" s="10" t="inlineStr">
         <is>
           <t>AJSS Platinum. Entry deadline: 12 Aug 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>10 Oct 2026</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>12 Oct 2026</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>US West Coast JCT 2026</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>National/Regional</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>27 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Danish Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>US Squash</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>Redwood Shores &amp; Redwood City, CA</t>
-        </is>
-      </c>
-      <c r="J34" s="6" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="K34" s="6" t="inlineStr">
-        <is>
-          <t>All junior age groups</t>
-        </is>
-      </c>
-      <c r="L34" s="6" t="inlineStr">
-        <is>
-          <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="29" t="inlineStr">
-        <is>
-          <t>13 Oct 2026</t>
-        </is>
-      </c>
-      <c r="B35" s="29" t="inlineStr">
-        <is>
-          <t>18 Oct 2026</t>
-        </is>
-      </c>
-      <c r="C35" s="29" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D35" s="30" t="inlineStr">
-        <is>
-          <t>Milo All Star Malaysia Squash Junior Open 2026 ★</t>
-        </is>
-      </c>
-      <c r="E35" s="30" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="F35" s="29" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G35" s="29" t="inlineStr"/>
-      <c r="H35" s="30" t="inlineStr">
-        <is>
-          <t>Squash Rackets Association of Malaysia / ASF</t>
-        </is>
-      </c>
-      <c r="I35" s="30" t="inlineStr">
-        <is>
-          <t>Kuala Lumpur, Malaysia</t>
-        </is>
-      </c>
-      <c r="J35" s="30" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="K35" s="30" t="inlineStr">
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>ESF / Danish Squash Federation</t>
+        </is>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>Herlev, Copenhagen, Denmark</t>
+        </is>
+      </c>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L35" s="30" t="inlineStr">
-        <is>
-          <t>AJSS Diamond — highest AJSS tier. Entry deadline: 14 Sep 2026 5pm Malaysian Time. Source: asiansquash.org/eventpage/ajss-event</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="25" t="inlineStr">
-        <is>
-          <t>22 Oct 2026</t>
-        </is>
-      </c>
-      <c r="B36" s="25" t="inlineStr">
-        <is>
-          <t>25 Oct 2026</t>
-        </is>
-      </c>
-      <c r="C36" s="25" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="D36" s="26" t="inlineStr">
-        <is>
-          <t>French Junior Open 2026</t>
-        </is>
-      </c>
-      <c r="E36" s="26" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="F36" s="25" t="inlineStr">
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Gold. Source: europeansquash.com/event/danish-junior-open-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>9 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="inlineStr">
+        <is>
+          <t>11 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C38" s="25" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
+        <is>
+          <t>Hungarian Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E38" s="26" t="inlineStr">
+        <is>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="F38" s="25" t="inlineStr">
         <is>
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="G36" s="25" t="inlineStr"/>
-      <c r="H36" s="26" t="inlineStr">
-        <is>
-          <t>ESF / French Squash Federation</t>
-        </is>
-      </c>
-      <c r="I36" s="26" t="inlineStr">
-        <is>
-          <t>France (venue TBC)</t>
-        </is>
-      </c>
-      <c r="J36" s="26" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="K36" s="26" t="inlineStr">
+      <c r="G38" s="25" t="inlineStr"/>
+      <c r="H38" s="26" t="inlineStr">
+        <is>
+          <t>ESF / Hungarian Squash Federation</t>
+        </is>
+      </c>
+      <c r="I38" s="26" t="inlineStr">
+        <is>
+          <t>Budapest, Hungary</t>
+        </is>
+      </c>
+      <c r="J38" s="26" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="K38" s="26" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L36" s="26" t="inlineStr">
-        <is>
-          <t>ESF Junior Circuit Gold. Venue not yet confirmed. Source: europeansquash.com/event/french-junior-open-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>24 Oct 2026</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="inlineStr">
-        <is>
-          <t>28 Oct 2026</t>
-        </is>
-      </c>
-      <c r="C37" s="11" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>Colombo Junior Squash Open 2026 ★</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="F37" s="11" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G37" s="11" t="inlineStr"/>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>Sri Lanka Squash / ASF</t>
-        </is>
-      </c>
-      <c r="I37" s="12" t="inlineStr">
-        <is>
-          <t>Ratmalana, Sri Lanka</t>
-        </is>
-      </c>
-      <c r="J37" s="12" t="inlineStr">
-        <is>
-          <t>Sri Lanka</t>
-        </is>
-      </c>
-      <c r="K37" s="12" t="inlineStr">
-        <is>
-          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
-        </is>
-      </c>
-      <c r="L37" s="12" t="inlineStr">
-        <is>
-          <t>AJSS Silver. Entry deadline: 23 Sep 2026 23:59 Sri Lanka Time. Source: asiansquash.org/eventpage/ajss-event</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>31 Oct 2026</t>
-        </is>
-      </c>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>15 Nov 2026</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>Hong Kong Junior Squash Championships 2026</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>National/Regional</t>
-        </is>
-      </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="inlineStr">
-        <is>
-          <t>25 Sep 2026</t>
-        </is>
-      </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>Squash Association of Hong Kong, China (HKSA)</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>Cornwall Street STTC &amp; Hong Kong Squash Centre, Hong Kong</t>
-        </is>
-      </c>
-      <c r="J38" s="6" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="K38" s="6" t="inlineStr">
-        <is>
-          <t>U9/U11/U13/U15/U17/U19 (B&amp;G)</t>
-        </is>
-      </c>
-      <c r="L38" s="6" t="inlineStr">
-        <is>
-          <t>HK Junior Ranking 3-star event. Played across 3 weekends: 31 Oct &amp; 1 Nov (CSPSC); 7-8 Nov (CSPSC); SF/Final 14-15 Nov (HKSC). Entry deadline: 25 Sep 2026. Source: hksquash.org.hk/public/tournaments/overview/id/391.html</t>
+      <c r="L38" s="26" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/hungarian-junior-open-2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>13 Nov 2026</t>
+          <t>10 Oct 2026</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>15 Nov 2026</t>
+          <t>12 Oct 2026</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>US Mid-Atlantic JCT 2026</t>
+          <t>US West Coast JCT 2026</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -22894,1488 +22901,2072 @@
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
+          <t>Redwood Shores &amp; Redwood City, CA</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>All junior age groups</t>
+        </is>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="29" t="inlineStr">
+        <is>
+          <t>13 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B40" s="29" t="inlineStr">
+        <is>
+          <t>18 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C40" s="29" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D40" s="30" t="inlineStr">
+        <is>
+          <t>Milo All Star Malaysia Squash Junior Open 2026 ★</t>
+        </is>
+      </c>
+      <c r="E40" s="30" t="inlineStr">
+        <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="F40" s="29" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G40" s="29" t="inlineStr"/>
+      <c r="H40" s="30" t="inlineStr">
+        <is>
+          <t>Squash Rackets Association of Malaysia / ASF</t>
+        </is>
+      </c>
+      <c r="I40" s="30" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur, Malaysia</t>
+        </is>
+      </c>
+      <c r="J40" s="30" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="K40" s="30" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L40" s="30" t="inlineStr">
+        <is>
+          <t>AJSS Diamond — highest AJSS tier. Entry deadline: 14 Sep 2026 5pm Malaysian Time. Source: asiansquash.org/eventpage/ajss-event</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>16 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>18 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C41" s="25" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D41" s="26" t="inlineStr">
+        <is>
+          <t>Romanian Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E41" s="26" t="inlineStr">
+        <is>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="F41" s="25" t="inlineStr">
+        <is>
+          <t>~ Estimated</t>
+        </is>
+      </c>
+      <c r="G41" s="25" t="inlineStr"/>
+      <c r="H41" s="26" t="inlineStr">
+        <is>
+          <t>ESF / Romanian Squash Federation</t>
+        </is>
+      </c>
+      <c r="I41" s="26" t="inlineStr">
+        <is>
+          <t>Bucharest, Romania</t>
+        </is>
+      </c>
+      <c r="J41" s="26" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="K41" s="26" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L41" s="26" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/romanian-junior-open-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>22 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>25 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr">
+        <is>
+          <t>French Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr"/>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>ESF / French Squash Federation</t>
+        </is>
+      </c>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>Wambrechies, France</t>
+        </is>
+      </c>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Gold. Entry deadline: 21 Sep 2026. Venue: P.A. du Chat, 75 rue Pierre et Marie Curie, 59118 Wambrechies. Source: europeansquash.com/event/french-junior-open-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="25" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>25 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C43" s="25" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="inlineStr">
+        <is>
+          <t>Lithuanian Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E43" s="26" t="inlineStr">
+        <is>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="F43" s="25" t="inlineStr">
+        <is>
+          <t>~ Estimated</t>
+        </is>
+      </c>
+      <c r="G43" s="25" t="inlineStr"/>
+      <c r="H43" s="26" t="inlineStr">
+        <is>
+          <t>ESF / Lithuanian Squash Federation</t>
+        </is>
+      </c>
+      <c r="I43" s="26" t="inlineStr">
+        <is>
+          <t>Kaunas, Lithuania</t>
+        </is>
+      </c>
+      <c r="J43" s="26" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="K43" s="26" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L43" s="26" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/lithuanian-junior-open-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>24 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>28 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>Colombo Junior Squash Open 2026 ★</t>
+        </is>
+      </c>
+      <c r="E44" s="12" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr"/>
+      <c r="H44" s="12" t="inlineStr">
+        <is>
+          <t>Sri Lanka Squash / ASF</t>
+        </is>
+      </c>
+      <c r="I44" s="12" t="inlineStr">
+        <is>
+          <t>Ratmalana, Sri Lanka</t>
+        </is>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr">
+        <is>
+          <t>AJSS Silver. Entry deadline: 23 Sep 2026 23:59 Sri Lanka Time. Source: asiansquash.org/eventpage/ajss-event</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>31 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>15 Nov 2026</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Hong Kong Junior Squash Championships 2026</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>National/Regional</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>25 Sep 2026</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Squash Association of Hong Kong, China (HKSA)</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>Cornwall Street STTC &amp; Hong Kong Squash Centre, Hong Kong</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>U9/U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>HK Junior Ranking 3-star event. Played across 3 weekends: 31 Oct &amp; 1 Nov (CSPSC); 7-8 Nov (CSPSC); SF/Final 14-15 Nov (HKSC). Entry deadline: 25 Sep 2026. Source: hksquash.org.hk/public/tournaments/overview/id/391.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>5 Nov 2026</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>8 Nov 2026</t>
+        </is>
+      </c>
+      <c r="C46" s="25" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
+        <is>
+          <t>Polish Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E46" s="26" t="inlineStr">
+        <is>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="F46" s="25" t="inlineStr">
+        <is>
+          <t>~ Estimated</t>
+        </is>
+      </c>
+      <c r="G46" s="25" t="inlineStr"/>
+      <c r="H46" s="26" t="inlineStr">
+        <is>
+          <t>ESF / Polish Squash Federation</t>
+        </is>
+      </c>
+      <c r="I46" s="26" t="inlineStr">
+        <is>
+          <t>Kraków, Poland</t>
+        </is>
+      </c>
+      <c r="J46" s="26" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="K46" s="26" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L46" s="26" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/polish-junior-open-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>13 Nov 2026</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>15 Nov 2026</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>US Mid-Atlantic JCT 2026</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>National/Regional</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>US Squash</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
           <t>Washington, D.C.</t>
         </is>
       </c>
-      <c r="J39" s="6" t="inlineStr">
+      <c r="J47" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K39" s="6" t="inlineStr">
+      <c r="K47" s="6" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="L39" s="6" t="inlineStr">
+      <c r="L47" s="6" t="inlineStr">
         <is>
           <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="25" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="25" t="inlineStr">
+        <is>
+          <t>13 Nov 2026</t>
+        </is>
+      </c>
+      <c r="B48" s="25" t="inlineStr">
+        <is>
+          <t>15 Nov 2026</t>
+        </is>
+      </c>
+      <c r="C48" s="25" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="inlineStr">
+        <is>
+          <t>Irish Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="F48" s="25" t="inlineStr">
+        <is>
+          <t>~ Estimated</t>
+        </is>
+      </c>
+      <c r="G48" s="25" t="inlineStr"/>
+      <c r="H48" s="26" t="inlineStr">
+        <is>
+          <t>ESF / Squash Ireland</t>
+        </is>
+      </c>
+      <c r="I48" s="26" t="inlineStr">
+        <is>
+          <t>Dublin, Ireland</t>
+        </is>
+      </c>
+      <c r="J48" s="26" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="K48" s="26" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L48" s="26" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Silver. Source: europeansquash.com/event/irish-junior-open-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="25" t="inlineStr">
         <is>
           <t>28 Nov 2026</t>
         </is>
       </c>
-      <c r="B40" s="25" t="inlineStr">
+      <c r="B49" s="25" t="inlineStr">
         <is>
           <t>30 Nov 2026</t>
         </is>
       </c>
-      <c r="C40" s="25" t="inlineStr">
+      <c r="C49" s="25" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D40" s="26" t="inlineStr">
+      <c r="D49" s="26" t="inlineStr">
         <is>
           <t>Malta Junior Open 2026</t>
         </is>
       </c>
-      <c r="E40" s="26" t="inlineStr">
+      <c r="E49" s="26" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F40" s="25" t="inlineStr">
+      <c r="F49" s="25" t="inlineStr">
         <is>
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="G40" s="25" t="inlineStr"/>
-      <c r="H40" s="26" t="inlineStr">
+      <c r="G49" s="25" t="inlineStr"/>
+      <c r="H49" s="26" t="inlineStr">
         <is>
           <t>ESF / Malta Squash</t>
         </is>
       </c>
-      <c r="I40" s="26" t="inlineStr">
+      <c r="I49" s="26" t="inlineStr">
         <is>
           <t>National Squash Centre, Malta</t>
         </is>
       </c>
-      <c r="J40" s="26" t="inlineStr">
+      <c r="J49" s="26" t="inlineStr">
         <is>
           <t>Malta</t>
         </is>
       </c>
-      <c r="K40" s="26" t="inlineStr">
+      <c r="K49" s="26" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L40" s="26" t="inlineStr">
+      <c r="L49" s="26" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Entry deadline: 20 Nov 2026 (exact event dates estimated). Source: europeansquash.com/event/malta-junior-open-2026</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>1 Dec 2026</t>
         </is>
       </c>
-      <c r="B41" s="9" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>6 Dec 2026</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D41" s="10" t="inlineStr">
+      <c r="D50" s="10" t="inlineStr">
         <is>
           <t>REDtone 18th KL Junior Open Squash Championships 2026 ★</t>
         </is>
       </c>
-      <c r="E41" s="10" t="inlineStr">
+      <c r="E50" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
+      <c r="F50" s="9" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G41" s="9" t="inlineStr"/>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="G50" s="9" t="inlineStr"/>
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>KL Squash / ASF</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="J41" s="10" t="inlineStr">
+      <c r="J50" s="10" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="K41" s="10" t="inlineStr">
+      <c r="K50" s="10" t="inlineStr">
         <is>
           <t>U9/U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L41" s="10" t="inlineStr">
+      <c r="L50" s="10" t="inlineStr">
         <is>
           <t>AJSS Platinum. Entry deadline: 1 Oct 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>8 Dec 2026</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>13 Dec 2026</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D42" s="10" t="inlineStr">
+      <c r="D51" s="10" t="inlineStr">
         <is>
           <t>ONCOCARE Singapore Junior Open 2026 ★</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr">
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="F51" s="9" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr"/>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="G51" s="9" t="inlineStr"/>
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>Singapore Squash Rackets Association (SSRA) / ASF</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="J42" s="10" t="inlineStr">
+      <c r="J51" s="10" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="K42" s="10" t="inlineStr">
+      <c r="K51" s="10" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L42" s="10" t="inlineStr">
+      <c r="L51" s="10" t="inlineStr">
         <is>
           <t>AJSS Platinum. Entry deadline: 1 Nov 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>12 Dec 2026</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>15 Dec 2026</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>Canadian Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr"/>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>Squash Canada</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>White Oaks Resort &amp; Spa, Niagara-on-the-Lake, Canada</t>
+        </is>
+      </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L52" s="10" t="inlineStr">
+        <is>
+          <t>30th anniversary edition. National top-tier event. Confirmed dates. Source: squash.ca/2026/06/2026-canadian-junior-open-dates-confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>19 Dec 2026</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>23 Dec 2026</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D43" s="10" t="inlineStr">
+      <c r="D53" s="10" t="inlineStr">
         <is>
           <t>US Junior Open 2026</t>
         </is>
       </c>
-      <c r="E43" s="10" t="inlineStr">
+      <c r="E53" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F53" s="9" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr"/>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="G53" s="9" t="inlineStr"/>
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="J43" s="10" t="inlineStr">
+      <c r="J53" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K43" s="10" t="inlineStr">
+      <c r="K53" s="10" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L43" s="10" t="inlineStr">
+      <c r="L53" s="10" t="inlineStr">
         <is>
           <t>One of the largest US junior squash events. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="25" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="25" t="inlineStr">
         <is>
           <t>20 Dec 2026</t>
         </is>
       </c>
-      <c r="B44" s="25" t="inlineStr">
+      <c r="B54" s="25" t="inlineStr">
         <is>
           <t>26 Dec 2026</t>
         </is>
       </c>
-      <c r="C44" s="25" t="inlineStr">
+      <c r="C54" s="25" t="inlineStr">
         <is>
           <t>Sun</t>
         </is>
       </c>
-      <c r="D44" s="26" t="inlineStr">
+      <c r="D54" s="26" t="inlineStr">
         <is>
           <t>HKFC International Junior Squash Open 2026 (est.)</t>
         </is>
       </c>
-      <c r="E44" s="26" t="inlineStr">
+      <c r="E54" s="26" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F44" s="25" t="inlineStr">
+      <c r="F54" s="25" t="inlineStr">
         <is>
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="G44" s="25" t="inlineStr"/>
-      <c r="H44" s="26" t="inlineStr">
+      <c r="G54" s="25" t="inlineStr"/>
+      <c r="H54" s="26" t="inlineStr">
         <is>
           <t>Squash Association of Hong Kong, China (HKSA)</t>
         </is>
       </c>
-      <c r="I44" s="26" t="inlineStr">
+      <c r="I54" s="26" t="inlineStr">
         <is>
           <t>Hong Kong Football Club &amp; HK Squash Centre, Hong Kong</t>
         </is>
       </c>
-      <c r="J44" s="26" t="inlineStr">
+      <c r="J54" s="26" t="inlineStr">
         <is>
           <t>Hong Kong</t>
         </is>
       </c>
-      <c r="K44" s="26" t="inlineStr">
+      <c r="K54" s="26" t="inlineStr">
         <is>
           <t>U9/U11/U13/U15/U17/U19 (B&amp;G — 12 categories)</t>
         </is>
       </c>
-      <c r="L44" s="26" t="inlineStr">
+      <c r="L54" s="26" t="inlineStr">
         <is>
           <t>AJSS Platinum. NOT YET listed on ASF page — dates estimated from prior years (2025 edition: 19-24 Dec 2025). Check hksquash.org.hk for official announcement.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
         <is>
           <t>28 Dec 2026</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B55" s="11" t="inlineStr">
         <is>
           <t>30 Dec 2026</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C55" s="11" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="D45" s="12" t="inlineStr">
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>Scottish Junior Open 2026</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E55" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="F55" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G45" s="11" t="inlineStr"/>
-      <c r="H45" s="12" t="inlineStr">
+      <c r="G55" s="11" t="inlineStr"/>
+      <c r="H55" s="12" t="inlineStr">
         <is>
           <t>ESF / Scottish Squash</t>
         </is>
       </c>
-      <c r="I45" s="12" t="inlineStr">
+      <c r="I55" s="12" t="inlineStr">
         <is>
           <t>Oriam &amp; Edinburgh Sports Club, Edinburgh</t>
         </is>
       </c>
-      <c r="J45" s="12" t="inlineStr">
+      <c r="J55" s="12" t="inlineStr">
         <is>
           <t>Scotland</t>
         </is>
       </c>
-      <c r="K45" s="12" t="inlineStr">
+      <c r="K55" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L45" s="12" t="inlineStr">
+      <c r="L55" s="12" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Silver. Lead-in event to British Junior Open 2027. Source: scottishsquash.org / europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>2 Jan 2027</t>
         </is>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B56" s="9" t="inlineStr">
         <is>
           <t>6 Jan 2027</t>
         </is>
       </c>
-      <c r="C46" s="9" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D46" s="10" t="inlineStr">
+      <c r="D56" s="10" t="inlineStr">
         <is>
           <t>British Junior Open 2027</t>
         </is>
       </c>
-      <c r="E46" s="10" t="inlineStr">
+      <c r="E56" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
+      <c r="F56" s="9" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr"/>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="G56" s="9" t="inlineStr"/>
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>England Squash / BJO</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>Birmingham, England</t>
         </is>
       </c>
-      <c r="J46" s="10" t="inlineStr">
+      <c r="J56" s="10" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="K46" s="10" t="inlineStr">
+      <c r="K56" s="10" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L46" s="10" t="inlineStr">
+      <c r="L56" s="10" t="inlineStr">
         <is>
           <t>Officially confirmed 2-6 Jan 2027. 750+ players from 50+ countries. Source: britishjunioropen.com/save-the-dates-british-junior-open-2027</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
         <is>
           <t>14 Jan 2027</t>
         </is>
       </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>17 Jan 2027</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D47" s="8" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>Czech Junior Open 2027</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr"/>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="G57" s="7" t="inlineStr"/>
+      <c r="H57" s="8" t="inlineStr">
         <is>
           <t>ESF / Czech Squash Federation</t>
         </is>
       </c>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="I57" s="8" t="inlineStr">
         <is>
           <t>Prague, Czech Republic</t>
         </is>
       </c>
-      <c r="J47" s="8" t="inlineStr">
+      <c r="J57" s="8" t="inlineStr">
         <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="K47" s="8" t="inlineStr">
+      <c r="K57" s="8" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L47" s="8" t="inlineStr">
+      <c r="L57" s="8" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Gold. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>16 Jan 2027</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>18 Jan 2027</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>US Connecticut JCT 2027</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F48" s="5" t="inlineStr">
+      <c r="F58" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="6" t="inlineStr">
+      <c r="G58" s="5" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I48" s="6" t="inlineStr">
+      <c r="I58" s="6" t="inlineStr">
         <is>
           <t>Stamford / Norwalk, CT</t>
         </is>
       </c>
-      <c r="J48" s="6" t="inlineStr">
+      <c r="J58" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K48" s="6" t="inlineStr">
+      <c r="K58" s="6" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="L48" s="6" t="inlineStr">
+      <c r="L58" s="6" t="inlineStr">
         <is>
           <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>29 Jan 2027</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>31 Jan 2027</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>Slovenia Junior Open 2027</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="F59" s="3" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr">
         <is>
           <t>ESF / Squash Slovenia</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr">
+      <c r="I59" s="4" t="inlineStr">
         <is>
           <t>Ljubljana, Slovenia</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr">
+      <c r="J59" s="4" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="K49" s="4" t="inlineStr">
+      <c r="K59" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L49" s="4" t="inlineStr">
+      <c r="L59" s="4" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>10 Feb 2027</t>
         </is>
       </c>
-      <c r="B50" s="11" t="inlineStr">
+      <c r="B60" s="11" t="inlineStr">
         <is>
           <t>14 Feb 2027</t>
         </is>
       </c>
-      <c r="C50" s="11" t="inlineStr">
+      <c r="C60" s="11" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>Sri Lanka Junior Squash Open 2027 ★</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E60" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F50" s="11" t="inlineStr">
+      <c r="F60" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G50" s="11" t="inlineStr"/>
-      <c r="H50" s="12" t="inlineStr">
+      <c r="G60" s="11" t="inlineStr"/>
+      <c r="H60" s="12" t="inlineStr">
         <is>
           <t>Sri Lanka Squash / ASF</t>
         </is>
       </c>
-      <c r="I50" s="12" t="inlineStr">
+      <c r="I60" s="12" t="inlineStr">
         <is>
           <t>Ratmalana, Sri Lanka</t>
         </is>
       </c>
-      <c r="J50" s="12" t="inlineStr">
+      <c r="J60" s="12" t="inlineStr">
         <is>
           <t>Sri Lanka</t>
         </is>
       </c>
-      <c r="K50" s="12" t="inlineStr">
+      <c r="K60" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L50" s="12" t="inlineStr">
+      <c r="L60" s="12" t="inlineStr">
         <is>
           <t>AJSS Silver. Entry deadline: 4 Jan 2027. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>11 Feb 2027</t>
         </is>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B61" s="11" t="inlineStr">
         <is>
           <t>14 Feb 2027</t>
         </is>
       </c>
-      <c r="C51" s="11" t="inlineStr">
+      <c r="C61" s="11" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D51" s="12" t="inlineStr">
+      <c r="D61" s="12" t="inlineStr">
         <is>
           <t>Swiss Junior Open 2027</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E61" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F51" s="11" t="inlineStr">
+      <c r="F61" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G51" s="11" t="inlineStr"/>
-      <c r="H51" s="12" t="inlineStr">
+      <c r="G61" s="11" t="inlineStr"/>
+      <c r="H61" s="12" t="inlineStr">
         <is>
           <t>ESF / Swiss Squash</t>
         </is>
       </c>
-      <c r="I51" s="12" t="inlineStr">
+      <c r="I61" s="12" t="inlineStr">
         <is>
           <t>Langnau am Albis, Switzerland</t>
         </is>
       </c>
-      <c r="J51" s="12" t="inlineStr">
+      <c r="J61" s="12" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="K51" s="12" t="inlineStr">
+      <c r="K61" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L51" s="12" t="inlineStr">
+      <c r="L61" s="12" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Silver. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>13 Feb 2027</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>15 Feb 2027</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr">
         <is>
           <t>US Texas JCT 2027</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E62" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F62" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr"/>
-      <c r="H52" s="6" t="inlineStr">
+      <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I52" s="6" t="inlineStr">
+      <c r="I62" s="6" t="inlineStr">
         <is>
           <t>Houston, TX</t>
         </is>
       </c>
-      <c r="J52" s="6" t="inlineStr">
+      <c r="J62" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K52" s="6" t="inlineStr">
+      <c r="K62" s="6" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="L52" s="6" t="inlineStr">
+      <c r="L62" s="6" t="inlineStr">
         <is>
           <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>18 Feb 2027</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>21 Feb 2027</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D53" s="8" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>German Junior Open 2027</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="E63" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="F53" s="7" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G53" s="7" t="inlineStr"/>
-      <c r="H53" s="8" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr"/>
+      <c r="H63" s="8" t="inlineStr">
         <is>
           <t>ESF / German Squash Federation</t>
         </is>
       </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="I63" s="8" t="inlineStr">
         <is>
           <t>Hamburg, Germany</t>
         </is>
       </c>
-      <c r="J53" s="8" t="inlineStr">
+      <c r="J63" s="8" t="inlineStr">
         <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="K53" s="8" t="inlineStr">
+      <c r="K63" s="8" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L53" s="8" t="inlineStr">
+      <c r="L63" s="8" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Gold. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>19 Feb 2027</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>21 Feb 2027</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr">
         <is>
           <t>US High School Championships 2027</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="E64" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F64" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="G64" s="5" t="inlineStr"/>
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I54" s="6" t="inlineStr">
+      <c r="I64" s="6" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="J54" s="6" t="inlineStr">
+      <c r="J64" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K54" s="6" t="inlineStr">
+      <c r="K64" s="6" t="inlineStr">
         <is>
           <t>High School age groups</t>
         </is>
       </c>
-      <c r="L54" s="6" t="inlineStr">
+      <c r="L64" s="6" t="inlineStr">
         <is>
           <t>US national high school squash championships. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="23" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="23" t="inlineStr">
         <is>
           <t>23 Feb 2027</t>
         </is>
       </c>
-      <c r="B55" s="23" t="inlineStr">
+      <c r="B65" s="23" t="inlineStr">
         <is>
           <t>27 Feb 2027</t>
         </is>
       </c>
-      <c r="C55" s="23" t="inlineStr">
+      <c r="C65" s="23" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D55" s="24" t="inlineStr">
+      <c r="D65" s="24" t="inlineStr">
         <is>
           <t>23rd Asian Junior Team Championships 2027</t>
         </is>
       </c>
-      <c r="E55" s="24" t="inlineStr">
+      <c r="E65" s="24" t="inlineStr">
         <is>
           <t>Asian Championship</t>
         </is>
       </c>
-      <c r="F55" s="23" t="inlineStr">
+      <c r="F65" s="23" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G55" s="23" t="inlineStr"/>
-      <c r="H55" s="24" t="inlineStr">
+      <c r="G65" s="23" t="inlineStr"/>
+      <c r="H65" s="24" t="inlineStr">
         <is>
           <t>Asian Squash Federation (ASF)</t>
         </is>
       </c>
-      <c r="I55" s="24" t="inlineStr">
+      <c r="I65" s="24" t="inlineStr">
         <is>
           <t>Thailand (venue TBC)</t>
         </is>
       </c>
-      <c r="J55" s="24" t="inlineStr">
+      <c r="J65" s="24" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="K55" s="24" t="inlineStr">
+      <c r="K65" s="24" t="inlineStr">
         <is>
           <t>U19 (B&amp;G — team format)</t>
         </is>
       </c>
-      <c r="L55" s="24" t="inlineStr">
+      <c r="L65" s="24" t="inlineStr">
         <is>
           <t>Confirmed on ASF 2026-27 calendar. Exact venue TBC. Source: asiansquash.org + thesquashsite.com</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>26 Feb 2027</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>28 Feb 2027</t>
         </is>
       </c>
-      <c r="C56" s="11" t="inlineStr">
+      <c r="C66" s="11" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D56" s="12" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>Austrian Junior Open 2027</t>
         </is>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="E66" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F56" s="11" t="inlineStr">
+      <c r="F66" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G56" s="11" t="inlineStr"/>
-      <c r="H56" s="12" t="inlineStr">
+      <c r="G66" s="11" t="inlineStr"/>
+      <c r="H66" s="12" t="inlineStr">
         <is>
           <t>ESF / Austrian Squash Federation</t>
         </is>
       </c>
-      <c r="I56" s="12" t="inlineStr">
+      <c r="I66" s="12" t="inlineStr">
         <is>
           <t>Vienna, Austria</t>
         </is>
       </c>
-      <c r="J56" s="12" t="inlineStr">
+      <c r="J66" s="12" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="K56" s="12" t="inlineStr">
+      <c r="K66" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L56" s="12" t="inlineStr">
+      <c r="L66" s="12" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Silver. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>12 Mar 2027</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
         <is>
           <t>US Junior Squash Championships 2027</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F57" s="5" t="inlineStr">
+      <c r="F67" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr"/>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="G67" s="5" t="inlineStr"/>
+      <c r="H67" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I57" s="6" t="inlineStr">
+      <c r="I67" s="6" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="J57" s="6" t="inlineStr">
+      <c r="J67" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K57" s="6" t="inlineStr">
+      <c r="K67" s="6" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L57" s="6" t="inlineStr">
+      <c r="L67" s="6" t="inlineStr">
         <is>
           <t>US national junior championships. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>12 Mar 2027</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>14 Mar 2027</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>Croatian Junior Open 2027</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr">
+      <c r="F68" s="3" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="4" t="inlineStr">
         <is>
           <t>ESF / Croatian Squash Federation</t>
         </is>
       </c>
-      <c r="I58" s="4" t="inlineStr">
+      <c r="I68" s="4" t="inlineStr">
         <is>
           <t>Zagreb, Croatia</t>
         </is>
       </c>
-      <c r="J58" s="4" t="inlineStr">
+      <c r="J68" s="4" t="inlineStr">
         <is>
           <t>Croatia</t>
         </is>
       </c>
-      <c r="K58" s="4" t="inlineStr">
+      <c r="K68" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L58" s="4" t="inlineStr">
+      <c r="L68" s="4" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="5" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>19 Mar 2027</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>21 Mar 2027</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>US Junior Divisional Championships 2027</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F59" s="5" t="inlineStr">
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G59" s="5" t="inlineStr"/>
-      <c r="H59" s="6" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr"/>
+      <c r="H69" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I59" s="6" t="inlineStr">
+      <c r="I69" s="6" t="inlineStr">
         <is>
           <t>USA (venue TBC)</t>
         </is>
       </c>
-      <c r="J59" s="6" t="inlineStr">
+      <c r="J69" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K59" s="6" t="inlineStr">
+      <c r="K69" s="6" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="L59" s="6" t="inlineStr">
+      <c r="L69" s="6" t="inlineStr">
         <is>
           <t>US Squash regional divisional event. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>19 Mar 2027</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>21 Mar 2027</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>Norwegian Junior Open 2027</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="F70" s="3" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr"/>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="4" t="inlineStr">
         <is>
           <t>ESF / Squash Norway</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr">
+      <c r="I70" s="4" t="inlineStr">
         <is>
           <t>Lysaker, Norway</t>
         </is>
       </c>
-      <c r="J60" s="4" t="inlineStr">
+      <c r="J70" s="4" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="K60" s="4" t="inlineStr">
+      <c r="K70" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L60" s="4" t="inlineStr">
+      <c r="L70" s="4" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="27" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="27" t="inlineStr">
         <is>
           <t>27 Mar 2027</t>
         </is>
       </c>
-      <c r="B61" s="27" t="inlineStr">
+      <c r="B71" s="27" t="inlineStr">
         <is>
           <t>4 Apr 2027</t>
         </is>
       </c>
-      <c r="C61" s="27" t="inlineStr">
+      <c r="C71" s="27" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D61" s="28" t="inlineStr">
+      <c r="D71" s="28" t="inlineStr">
         <is>
           <t>PSA World Championships 2026-27</t>
         </is>
       </c>
-      <c r="E61" s="28" t="inlineStr">
+      <c r="E71" s="28" t="inlineStr">
         <is>
           <t>World Championship</t>
         </is>
       </c>
-      <c r="F61" s="27" t="inlineStr">
+      <c r="F71" s="27" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G61" s="27" t="inlineStr"/>
-      <c r="H61" s="28" t="inlineStr">
+      <c r="G71" s="27" t="inlineStr"/>
+      <c r="H71" s="28" t="inlineStr">
         <is>
           <t>PSA World Tour / England Squash</t>
         </is>
       </c>
-      <c r="I61" s="28" t="inlineStr">
+      <c r="I71" s="28" t="inlineStr">
         <is>
           <t>London, England</t>
         </is>
       </c>
-      <c r="J61" s="28" t="inlineStr">
+      <c r="J71" s="28" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="K61" s="28" t="inlineStr">
+      <c r="K71" s="28" t="inlineStr">
         <is>
           <t>Open (professional)</t>
         </is>
       </c>
-      <c r="L61" s="28" t="inlineStr">
+      <c r="L71" s="28" t="inlineStr">
         <is>
           <t>Professional event — included for reference. Source: worldsquashchamps.com</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="27" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="27" t="inlineStr">
         <is>
           <t>7 Jun 2027</t>
         </is>
       </c>
-      <c r="B62" s="27" t="inlineStr">
+      <c r="B72" s="27" t="inlineStr">
         <is>
           <t>13 Jun 2027</t>
         </is>
       </c>
-      <c r="C62" s="27" t="inlineStr">
+      <c r="C72" s="27" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="D62" s="28" t="inlineStr">
+      <c r="D72" s="28" t="inlineStr">
         <is>
           <t>WSF World Under-23 Championships 2027</t>
         </is>
       </c>
-      <c r="E62" s="28" t="inlineStr">
+      <c r="E72" s="28" t="inlineStr">
         <is>
           <t>World Championship</t>
         </is>
       </c>
-      <c r="F62" s="27" t="inlineStr">
+      <c r="F72" s="27" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G62" s="27" t="inlineStr"/>
-      <c r="H62" s="28" t="inlineStr">
+      <c r="G72" s="27" t="inlineStr"/>
+      <c r="H72" s="28" t="inlineStr">
         <is>
           <t>World Squash Federation (WSF)</t>
         </is>
       </c>
-      <c r="I62" s="28" t="inlineStr">
+      <c r="I72" s="28" t="inlineStr">
         <is>
           <t>Karachi, Pakistan</t>
         </is>
       </c>
-      <c r="J62" s="28" t="inlineStr">
+      <c r="J72" s="28" t="inlineStr">
         <is>
           <t>Pakistan</t>
         </is>
       </c>
-      <c r="K62" s="28" t="inlineStr">
+      <c r="K72" s="28" t="inlineStr">
         <is>
           <t>U23 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L62" s="28" t="inlineStr">
+      <c r="L72" s="28" t="inlineStr">
         <is>
           <t>WSF global event for under-23 players. Source: worldsquash.sport</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="31" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
         <is>
           <t>COLOUR KEY — AJSS Levels: Diamond &gt; Platinum &gt; Gold &gt; Silver &gt; Bronze</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="28" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="28" t="inlineStr">
         <is>
           <t>World Championship</t>
         </is>
       </c>
-      <c r="B65" s="28" t="inlineStr">
+      <c r="B75" s="28" t="inlineStr">
         <is>
           <t>WSF / PSA global championship — pinnacle events</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="24" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="24" t="inlineStr">
         <is>
           <t>Asian Championship</t>
         </is>
       </c>
-      <c r="B66" s="24" t="inlineStr">
+      <c r="B76" s="24" t="inlineStr">
         <is>
           <t>ASF continental championships (Asian Junior Individual &amp; Team)</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>AJSS Diamond — highest AJSS tier (e.g. Milo Malaysia)</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="10" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="B68" s="10" t="inlineStr">
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>AJSS Platinum / ESF Platinum — highest open tier (HK Junior, BJO, Singapore JO, KL JO, Indian JO)</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="8" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>AJSS Gold / ESF Gold — second tier (Korea, Japan, Penang, Lion City, Slams, Dutch JO, German JO)</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="12" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B80" s="12" t="inlineStr">
         <is>
           <t>AJSS Silver / ESF Silver — third tier (Sri Lanka, Australia, China, Qatar, Chinese Taipei, Swiss JO)</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>ESF Bronze — fourth tier European circuit (Slovenia, Croatia, Norway)</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>National tour stops and domestic championships (US Squash JCT / High School / Divisional)</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="26" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="26" t="inlineStr">
         <is>
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="B73" s="26" t="inlineStr">
+      <c r="B83" s="26" t="inlineStr">
         <is>
           <t>AMBER = dates not yet officially confirmed — verify with the relevant federation before travel/planning</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:L62"/>
+  <autoFilter ref="A2:L72"/>
   <mergeCells count="11">
-    <mergeCell ref="B65:L65"/>
-    <mergeCell ref="A64:L64"/>
-    <mergeCell ref="B73:L73"/>
-    <mergeCell ref="B70:L70"/>
-    <mergeCell ref="B68:L68"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="B75:L75"/>
+    <mergeCell ref="B82:L82"/>
+    <mergeCell ref="B78:L78"/>
+    <mergeCell ref="B77:L77"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="B69:L69"/>
-    <mergeCell ref="B72:L72"/>
-    <mergeCell ref="B66:L66"/>
-    <mergeCell ref="B67:L67"/>
-    <mergeCell ref="B71:L71"/>
+    <mergeCell ref="B80:L80"/>
+    <mergeCell ref="B81:L81"/>
+    <mergeCell ref="A74:L74"/>
+    <mergeCell ref="B76:L76"/>
+    <mergeCell ref="B79:L79"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Holiday_Calendar_2026_2027.xlsx
+++ b/Holiday_Calendar_2026_2027.xlsx
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Hong Kong'!$A$2:$H$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Singapore'!$A$2:$H$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'China'!$A$2:$H$76</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Squash Junior Events'!$A$2:$L$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Squash Junior Events'!$A$2:$L$74</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20688,7 +20688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L83"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -22633,12 +22633,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>18 Sep 2026</t>
+          <t>11 Sep 2026</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>20 Sep 2026</t>
+          <t>13 Sep 2026</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -22648,7 +22648,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Slovak Junior Open 2026</t>
+          <t>Estonian Junior Open 2026</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -22664,676 +22664,672 @@
       <c r="G35" s="3" t="inlineStr"/>
       <c r="H35" s="4" t="inlineStr">
         <is>
+          <t>ESF / Estonian Squash Federation</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>YOLO Squash, Tallinn, Estonia</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Bronze — inaugural edition. Estonia joins European junior calendar for first time. Source: europeansquash.com/event/estonian-junior-open-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>18 Sep 2026</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Slovak Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
           <t>ESF / Slovak Squash Federation</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>Bratislava, Slovakia</t>
         </is>
       </c>
-      <c r="J35" s="4" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr">
         <is>
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr">
+      <c r="L36" s="4" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/slovak-junior-open-2026</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>19 Sep 2026</t>
         </is>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>24 Sep 2026</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D37" s="10" t="inlineStr">
         <is>
           <t>Indian Junior Open 2026 ★</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
+      <c r="E37" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F37" s="9" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="G37" s="9" t="inlineStr"/>
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>Squash Rackets Federation of India / ASF</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>Kolkata, India</t>
         </is>
       </c>
-      <c r="J36" s="10" t="inlineStr">
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>India</t>
         </is>
       </c>
-      <c r="K36" s="10" t="inlineStr">
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L36" s="10" t="inlineStr">
+      <c r="L37" s="10" t="inlineStr">
         <is>
           <t>AJSS Platinum. Entry deadline: 12 Aug 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>24 Sep 2026</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>27 Sep 2026</t>
         </is>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D37" s="8" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>Danish Junior Open 2026</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="8" t="inlineStr">
+      <c r="G38" s="7" t="inlineStr"/>
+      <c r="H38" s="8" t="inlineStr">
         <is>
           <t>ESF / Danish Squash Federation</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="I38" s="8" t="inlineStr">
         <is>
           <t>Herlev, Copenhagen, Denmark</t>
         </is>
       </c>
-      <c r="J37" s="8" t="inlineStr">
+      <c r="J38" s="8" t="inlineStr">
         <is>
           <t>Denmark</t>
         </is>
       </c>
-      <c r="K37" s="8" t="inlineStr">
+      <c r="K38" s="8" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L37" s="8" t="inlineStr">
+      <c r="L38" s="8" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Gold. Source: europeansquash.com/event/danish-junior-open-2026</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="25" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="25" t="inlineStr">
         <is>
           <t>9 Oct 2026</t>
         </is>
       </c>
-      <c r="B38" s="25" t="inlineStr">
+      <c r="B39" s="25" t="inlineStr">
         <is>
           <t>11 Oct 2026</t>
         </is>
       </c>
-      <c r="C38" s="25" t="inlineStr">
+      <c r="C39" s="25" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D38" s="26" t="inlineStr">
+      <c r="D39" s="26" t="inlineStr">
         <is>
           <t>Hungarian Junior Open 2026</t>
         </is>
       </c>
-      <c r="E38" s="26" t="inlineStr">
+      <c r="E39" s="26" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F38" s="25" t="inlineStr">
+      <c r="F39" s="25" t="inlineStr">
         <is>
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="G38" s="25" t="inlineStr"/>
-      <c r="H38" s="26" t="inlineStr">
+      <c r="G39" s="25" t="inlineStr"/>
+      <c r="H39" s="26" t="inlineStr">
         <is>
           <t>ESF / Hungarian Squash Federation</t>
         </is>
       </c>
-      <c r="I38" s="26" t="inlineStr">
+      <c r="I39" s="26" t="inlineStr">
         <is>
           <t>Budapest, Hungary</t>
         </is>
       </c>
-      <c r="J38" s="26" t="inlineStr">
+      <c r="J39" s="26" t="inlineStr">
         <is>
           <t>Hungary</t>
         </is>
       </c>
-      <c r="K38" s="26" t="inlineStr">
+      <c r="K39" s="26" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L38" s="26" t="inlineStr">
+      <c r="L39" s="26" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/hungarian-junior-open-2026</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>10 Oct 2026</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>12 Oct 2026</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>US West Coast JCT 2026</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I39" s="6" t="inlineStr">
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>Redwood Shores &amp; Redwood City, CA</t>
         </is>
       </c>
-      <c r="J39" s="6" t="inlineStr">
+      <c r="J40" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K39" s="6" t="inlineStr">
+      <c r="K40" s="6" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="L39" s="6" t="inlineStr">
+      <c r="L40" s="6" t="inlineStr">
         <is>
           <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="29" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="29" t="inlineStr">
         <is>
           <t>13 Oct 2026</t>
         </is>
       </c>
-      <c r="B40" s="29" t="inlineStr">
+      <c r="B41" s="29" t="inlineStr">
         <is>
           <t>18 Oct 2026</t>
         </is>
       </c>
-      <c r="C40" s="29" t="inlineStr">
+      <c r="C41" s="29" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D40" s="30" t="inlineStr">
+      <c r="D41" s="30" t="inlineStr">
         <is>
           <t>Milo All Star Malaysia Squash Junior Open 2026 ★</t>
         </is>
       </c>
-      <c r="E40" s="30" t="inlineStr">
+      <c r="E41" s="30" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="F40" s="29" t="inlineStr">
+      <c r="F41" s="29" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G40" s="29" t="inlineStr"/>
-      <c r="H40" s="30" t="inlineStr">
+      <c r="G41" s="29" t="inlineStr"/>
+      <c r="H41" s="30" t="inlineStr">
         <is>
           <t>Squash Rackets Association of Malaysia / ASF</t>
         </is>
       </c>
-      <c r="I40" s="30" t="inlineStr">
+      <c r="I41" s="30" t="inlineStr">
         <is>
           <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
-      <c r="J40" s="30" t="inlineStr">
+      <c r="J41" s="30" t="inlineStr">
         <is>
           <t>Malaysia</t>
         </is>
       </c>
-      <c r="K40" s="30" t="inlineStr">
+      <c r="K41" s="30" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L40" s="30" t="inlineStr">
+      <c r="L41" s="30" t="inlineStr">
         <is>
           <t>AJSS Diamond — highest AJSS tier. Entry deadline: 14 Sep 2026 5pm Malaysian Time. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="25" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="25" t="inlineStr">
         <is>
           <t>16 Oct 2026</t>
         </is>
       </c>
-      <c r="B41" s="25" t="inlineStr">
+      <c r="B42" s="25" t="inlineStr">
         <is>
           <t>18 Oct 2026</t>
         </is>
       </c>
-      <c r="C41" s="25" t="inlineStr">
+      <c r="C42" s="25" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D41" s="26" t="inlineStr">
+      <c r="D42" s="26" t="inlineStr">
         <is>
           <t>Romanian Junior Open 2026</t>
         </is>
       </c>
-      <c r="E41" s="26" t="inlineStr">
+      <c r="E42" s="26" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F41" s="25" t="inlineStr">
+      <c r="F42" s="25" t="inlineStr">
         <is>
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="G41" s="25" t="inlineStr"/>
-      <c r="H41" s="26" t="inlineStr">
+      <c r="G42" s="25" t="inlineStr"/>
+      <c r="H42" s="26" t="inlineStr">
         <is>
           <t>ESF / Romanian Squash Federation</t>
         </is>
       </c>
-      <c r="I41" s="26" t="inlineStr">
+      <c r="I42" s="26" t="inlineStr">
         <is>
           <t>Bucharest, Romania</t>
         </is>
       </c>
-      <c r="J41" s="26" t="inlineStr">
+      <c r="J42" s="26" t="inlineStr">
         <is>
           <t>Romania</t>
         </is>
       </c>
-      <c r="K41" s="26" t="inlineStr">
+      <c r="K42" s="26" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L41" s="26" t="inlineStr">
+      <c r="L42" s="26" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/romanian-junior-open-2026</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>22 Oct 2026</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>25 Oct 2026</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
+      <c r="D43" s="8" t="inlineStr">
         <is>
           <t>French Junior Open 2026</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="8" t="inlineStr">
+      <c r="G43" s="7" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr">
         <is>
           <t>ESF / French Squash Federation</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>Wambrechies, France</t>
         </is>
       </c>
-      <c r="J42" s="8" t="inlineStr">
+      <c r="J43" s="8" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="K42" s="8" t="inlineStr">
+      <c r="K43" s="8" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L42" s="8" t="inlineStr">
+      <c r="L43" s="8" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Gold. Entry deadline: 21 Sep 2026. Venue: P.A. du Chat, 75 rue Pierre et Marie Curie, 59118 Wambrechies. Source: europeansquash.com/event/french-junior-open-2026</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="25" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="25" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
       </c>
-      <c r="B43" s="25" t="inlineStr">
+      <c r="B44" s="25" t="inlineStr">
         <is>
           <t>25 Oct 2026</t>
         </is>
       </c>
-      <c r="C43" s="25" t="inlineStr">
+      <c r="C44" s="25" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D43" s="26" t="inlineStr">
+      <c r="D44" s="26" t="inlineStr">
         <is>
           <t>Lithuanian Junior Open 2026</t>
         </is>
       </c>
-      <c r="E43" s="26" t="inlineStr">
+      <c r="E44" s="26" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F43" s="25" t="inlineStr">
+      <c r="F44" s="25" t="inlineStr">
         <is>
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="G43" s="25" t="inlineStr"/>
-      <c r="H43" s="26" t="inlineStr">
+      <c r="G44" s="25" t="inlineStr"/>
+      <c r="H44" s="26" t="inlineStr">
         <is>
           <t>ESF / Lithuanian Squash Federation</t>
         </is>
       </c>
-      <c r="I43" s="26" t="inlineStr">
+      <c r="I44" s="26" t="inlineStr">
         <is>
           <t>Kaunas, Lithuania</t>
         </is>
       </c>
-      <c r="J43" s="26" t="inlineStr">
+      <c r="J44" s="26" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="K43" s="26" t="inlineStr">
+      <c r="K44" s="26" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L43" s="26" t="inlineStr">
+      <c r="L44" s="26" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/lithuanian-junior-open-2026</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>24 Oct 2026</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>28 Oct 2026</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C45" s="11" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t>Colombo Junior Squash Open 2026 ★</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="F45" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G44" s="11" t="inlineStr"/>
-      <c r="H44" s="12" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr"/>
+      <c r="H45" s="12" t="inlineStr">
         <is>
           <t>Sri Lanka Squash / ASF</t>
         </is>
       </c>
-      <c r="I44" s="12" t="inlineStr">
+      <c r="I45" s="12" t="inlineStr">
         <is>
           <t>Ratmalana, Sri Lanka</t>
         </is>
       </c>
-      <c r="J44" s="12" t="inlineStr">
+      <c r="J45" s="12" t="inlineStr">
         <is>
           <t>Sri Lanka</t>
         </is>
       </c>
-      <c r="K44" s="12" t="inlineStr">
+      <c r="K45" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L44" s="12" t="inlineStr">
+      <c r="L45" s="12" t="inlineStr">
         <is>
           <t>AJSS Silver. Entry deadline: 23 Sep 2026 23:59 Sri Lanka Time. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>31 Oct 2026</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>15 Nov 2026</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>Hong Kong Junior Squash Championships 2026</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>29 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>1 Nov 2026</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Squash Travel by Nirvana British Junior Championships 2026</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F45" s="5" t="inlineStr">
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>25 Sep 2026</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>Squash Association of Hong Kong, China (HKSA)</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>Cornwall Street STTC &amp; Hong Kong Squash Centre, Hong Kong</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>Hong Kong</t>
-        </is>
-      </c>
-      <c r="K45" s="6" t="inlineStr">
-        <is>
-          <t>U9/U11/U13/U15/U17/U19 (B&amp;G)</t>
-        </is>
-      </c>
-      <c r="L45" s="6" t="inlineStr">
-        <is>
-          <t>HK Junior Ranking 3-star event. Played across 3 weekends: 31 Oct &amp; 1 Nov (CSPSC); 7-8 Nov (CSPSC); SF/Final 14-15 Nov (HKSC). Entry deadline: 25 Sep 2026. Source: hksquash.org.hk/public/tournaments/overview/id/391.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>5 Nov 2026</t>
-        </is>
-      </c>
-      <c r="B46" s="25" t="inlineStr">
-        <is>
-          <t>8 Nov 2026</t>
-        </is>
-      </c>
-      <c r="C46" s="25" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="D46" s="26" t="inlineStr">
-        <is>
-          <t>Polish Junior Open 2026</t>
-        </is>
-      </c>
-      <c r="E46" s="26" t="inlineStr">
-        <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="F46" s="25" t="inlineStr">
-        <is>
-          <t>~ Estimated</t>
-        </is>
-      </c>
-      <c r="G46" s="25" t="inlineStr"/>
-      <c r="H46" s="26" t="inlineStr">
-        <is>
-          <t>ESF / Polish Squash Federation</t>
-        </is>
-      </c>
-      <c r="I46" s="26" t="inlineStr">
-        <is>
-          <t>Kraków, Poland</t>
-        </is>
-      </c>
-      <c r="J46" s="26" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-      <c r="K46" s="26" t="inlineStr">
-        <is>
-          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
-        </is>
-      </c>
-      <c r="L46" s="26" t="inlineStr">
-        <is>
-          <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/polish-junior-open-2026</t>
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>England Squash</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>Sheffield, England</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>All junior age groups (UK players)</t>
+        </is>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>52nd edition. UK national junior championships — top UK talent. Source: englandsquash.com/news/dates-announced-for-2026-british-junior-championships</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>13 Nov 2026</t>
+          <t>31 Oct 2026</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -23343,12 +23339,12 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>US Mid-Atlantic JCT 2026</t>
+          <t>Hong Kong Junior Squash Championships 2026</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -23361,57 +23357,61 @@
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr"/>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>25 Sep 2026</t>
+        </is>
+      </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>US Squash</t>
+          <t>Squash Association of Hong Kong, China (HKSA)</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>Washington, D.C.</t>
+          <t>Cornwall Street STTC &amp; Hong Kong Squash Centre, Hong Kong</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>All junior age groups</t>
+          <t>U9/U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
+          <t>HK Junior Ranking 3-star event. Played across 3 weekends: 31 Oct &amp; 1 Nov (CSPSC); 7-8 Nov (CSPSC); SF/Final 14-15 Nov (HKSC). Entry deadline: 25 Sep 2026. Source: hksquash.org.hk/public/tournaments/overview/id/391.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>13 Nov 2026</t>
+          <t>5 Nov 2026</t>
         </is>
       </c>
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>15 Nov 2026</t>
+          <t>8 Nov 2026</t>
         </is>
       </c>
       <c r="C48" s="25" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="D48" s="26" t="inlineStr">
         <is>
-          <t>Irish Junior Open 2026</t>
+          <t>Polish Junior Open 2026</t>
         </is>
       </c>
       <c r="E48" s="26" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="F48" s="25" t="inlineStr">
@@ -23422,223 +23422,223 @@
       <c r="G48" s="25" t="inlineStr"/>
       <c r="H48" s="26" t="inlineStr">
         <is>
+          <t>ESF / Polish Squash Federation</t>
+        </is>
+      </c>
+      <c r="I48" s="26" t="inlineStr">
+        <is>
+          <t>Kraków, Poland</t>
+        </is>
+      </c>
+      <c r="J48" s="26" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="K48" s="26" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L48" s="26" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/polish-junior-open-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>13 Nov 2026</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>15 Nov 2026</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>US Mid-Atlantic JCT 2026</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>National/Regional</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr">
+        <is>
+          <t>US Squash</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>Washington, D.C.</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>All junior age groups</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>13 Nov 2026</t>
+        </is>
+      </c>
+      <c r="B50" s="25" t="inlineStr">
+        <is>
+          <t>15 Nov 2026</t>
+        </is>
+      </c>
+      <c r="C50" s="25" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="inlineStr">
+        <is>
+          <t>Irish Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E50" s="26" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="F50" s="25" t="inlineStr">
+        <is>
+          <t>~ Estimated</t>
+        </is>
+      </c>
+      <c r="G50" s="25" t="inlineStr"/>
+      <c r="H50" s="26" t="inlineStr">
+        <is>
           <t>ESF / Squash Ireland</t>
         </is>
       </c>
-      <c r="I48" s="26" t="inlineStr">
+      <c r="I50" s="26" t="inlineStr">
         <is>
           <t>Dublin, Ireland</t>
         </is>
       </c>
-      <c r="J48" s="26" t="inlineStr">
+      <c r="J50" s="26" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="K48" s="26" t="inlineStr">
+      <c r="K50" s="26" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L48" s="26" t="inlineStr">
+      <c r="L50" s="26" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Silver. Source: europeansquash.com/event/irish-junior-open-2026</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="25" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="25" t="inlineStr">
         <is>
           <t>28 Nov 2026</t>
         </is>
       </c>
-      <c r="B49" s="25" t="inlineStr">
+      <c r="B51" s="25" t="inlineStr">
         <is>
           <t>30 Nov 2026</t>
         </is>
       </c>
-      <c r="C49" s="25" t="inlineStr">
+      <c r="C51" s="25" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D49" s="26" t="inlineStr">
+      <c r="D51" s="26" t="inlineStr">
         <is>
           <t>Malta Junior Open 2026</t>
         </is>
       </c>
-      <c r="E49" s="26" t="inlineStr">
+      <c r="E51" s="26" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F49" s="25" t="inlineStr">
+      <c r="F51" s="25" t="inlineStr">
         <is>
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="G49" s="25" t="inlineStr"/>
-      <c r="H49" s="26" t="inlineStr">
+      <c r="G51" s="25" t="inlineStr"/>
+      <c r="H51" s="26" t="inlineStr">
         <is>
           <t>ESF / Malta Squash</t>
         </is>
       </c>
-      <c r="I49" s="26" t="inlineStr">
+      <c r="I51" s="26" t="inlineStr">
         <is>
           <t>National Squash Centre, Malta</t>
         </is>
       </c>
-      <c r="J49" s="26" t="inlineStr">
+      <c r="J51" s="26" t="inlineStr">
         <is>
           <t>Malta</t>
         </is>
       </c>
-      <c r="K49" s="26" t="inlineStr">
+      <c r="K51" s="26" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L49" s="26" t="inlineStr">
+      <c r="L51" s="26" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Entry deadline: 20 Nov 2026 (exact event dates estimated). Source: europeansquash.com/event/malta-junior-open-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
-        <is>
-          <t>1 Dec 2026</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>6 Dec 2026</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>REDtone 18th KL Junior Open Squash Championships 2026 ★</t>
-        </is>
-      </c>
-      <c r="E50" s="10" t="inlineStr">
-        <is>
-          <t>Platinum</t>
-        </is>
-      </c>
-      <c r="F50" s="9" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G50" s="9" t="inlineStr"/>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>KL Squash / ASF</t>
-        </is>
-      </c>
-      <c r="I50" s="10" t="inlineStr">
-        <is>
-          <t>Kuala Lumpur, Malaysia</t>
-        </is>
-      </c>
-      <c r="J50" s="10" t="inlineStr">
-        <is>
-          <t>Malaysia</t>
-        </is>
-      </c>
-      <c r="K50" s="10" t="inlineStr">
-        <is>
-          <t>U9/U11/U13/U15/U17/U19 (B&amp;G)</t>
-        </is>
-      </c>
-      <c r="L50" s="10" t="inlineStr">
-        <is>
-          <t>AJSS Platinum. Entry deadline: 1 Oct 2026. Source: asiansquash.org/eventpage/ajss-event</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>8 Dec 2026</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>13 Dec 2026</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>Tue</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>ONCOCARE Singapore Junior Open 2026 ★</t>
-        </is>
-      </c>
-      <c r="E51" s="10" t="inlineStr">
-        <is>
-          <t>Platinum</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="inlineStr"/>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>Singapore Squash Rackets Association (SSRA) / ASF</t>
-        </is>
-      </c>
-      <c r="I51" s="10" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="J51" s="10" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="K51" s="10" t="inlineStr">
-        <is>
-          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
-        </is>
-      </c>
-      <c r="L51" s="10" t="inlineStr">
-        <is>
-          <t>AJSS Platinum. Entry deadline: 1 Nov 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>12 Dec 2026</t>
+          <t>1 Dec 2026</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>15 Dec 2026</t>
+          <t>6 Dec 2026</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Canadian Junior Open 2026</t>
+          <t>REDtone 18th KL Junior Open Squash Championships 2026 ★</t>
         </is>
       </c>
       <c r="E52" s="10" t="inlineStr">
@@ -23654,49 +23654,49 @@
       <c r="G52" s="9" t="inlineStr"/>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>Squash Canada</t>
+          <t>KL Squash / ASF</t>
         </is>
       </c>
       <c r="I52" s="10" t="inlineStr">
         <is>
-          <t>White Oaks Resort &amp; Spa, Niagara-on-the-Lake, Canada</t>
+          <t>Kuala Lumpur, Malaysia</t>
         </is>
       </c>
       <c r="J52" s="10" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="K52" s="10" t="inlineStr">
         <is>
-          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+          <t>U9/U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
       <c r="L52" s="10" t="inlineStr">
         <is>
-          <t>30th anniversary edition. National top-tier event. Confirmed dates. Source: squash.ca/2026/06/2026-canadian-junior-open-dates-confirmed</t>
+          <t>AJSS Platinum. Entry deadline: 1 Oct 2026. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>19 Dec 2026</t>
+          <t>8 Dec 2026</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>23 Dec 2026</t>
+          <t>13 Dec 2026</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Sat</t>
+          <t>Tue</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>US Junior Open 2026</t>
+          <t>ONCOCARE Singapore Junior Open 2026 ★</t>
         </is>
       </c>
       <c r="E53" s="10" t="inlineStr">
@@ -23712,629 +23712,629 @@
       <c r="G53" s="9" t="inlineStr"/>
       <c r="H53" s="10" t="inlineStr">
         <is>
+          <t>Singapore Squash Rackets Association (SSRA) / ASF</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="J53" s="10" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="K53" s="10" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L53" s="10" t="inlineStr">
+        <is>
+          <t>AJSS Platinum. Entry deadline: 1 Nov 2026. Source: asiansquash.org/eventpage/ajss-event</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>12 Dec 2026</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>15 Dec 2026</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>Canadian Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="inlineStr"/>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>Squash Canada</t>
+        </is>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>White Oaks Resort &amp; Spa, Niagara-on-the-Lake, Canada</t>
+        </is>
+      </c>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="K54" s="10" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L54" s="10" t="inlineStr">
+        <is>
+          <t>30th anniversary edition. National top-tier event. Confirmed dates. Source: squash.ca/2026/06/2026-canadian-junior-open-dates-confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>19 Dec 2026</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>23 Dec 2026</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Sat</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>US Junior Open 2026</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="inlineStr"/>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="J53" s="10" t="inlineStr">
+      <c r="J55" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K53" s="10" t="inlineStr">
+      <c r="K55" s="10" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L53" s="10" t="inlineStr">
+      <c r="L55" s="10" t="inlineStr">
         <is>
           <t>One of the largest US junior squash events. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="25" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="25" t="inlineStr">
         <is>
           <t>20 Dec 2026</t>
         </is>
       </c>
-      <c r="B54" s="25" t="inlineStr">
+      <c r="B56" s="25" t="inlineStr">
         <is>
           <t>26 Dec 2026</t>
         </is>
       </c>
-      <c r="C54" s="25" t="inlineStr">
+      <c r="C56" s="25" t="inlineStr">
         <is>
           <t>Sun</t>
         </is>
       </c>
-      <c r="D54" s="26" t="inlineStr">
+      <c r="D56" s="26" t="inlineStr">
         <is>
           <t>HKFC International Junior Squash Open 2026 (est.)</t>
         </is>
       </c>
-      <c r="E54" s="26" t="inlineStr">
+      <c r="E56" s="26" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F54" s="25" t="inlineStr">
+      <c r="F56" s="25" t="inlineStr">
         <is>
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="G54" s="25" t="inlineStr"/>
-      <c r="H54" s="26" t="inlineStr">
+      <c r="G56" s="25" t="inlineStr"/>
+      <c r="H56" s="26" t="inlineStr">
         <is>
           <t>Squash Association of Hong Kong, China (HKSA)</t>
         </is>
       </c>
-      <c r="I54" s="26" t="inlineStr">
+      <c r="I56" s="26" t="inlineStr">
         <is>
           <t>Hong Kong Football Club &amp; HK Squash Centre, Hong Kong</t>
         </is>
       </c>
-      <c r="J54" s="26" t="inlineStr">
+      <c r="J56" s="26" t="inlineStr">
         <is>
           <t>Hong Kong</t>
         </is>
       </c>
-      <c r="K54" s="26" t="inlineStr">
+      <c r="K56" s="26" t="inlineStr">
         <is>
           <t>U9/U11/U13/U15/U17/U19 (B&amp;G — 12 categories)</t>
         </is>
       </c>
-      <c r="L54" s="26" t="inlineStr">
+      <c r="L56" s="26" t="inlineStr">
         <is>
           <t>AJSS Platinum. NOT YET listed on ASF page — dates estimated from prior years (2025 edition: 19-24 Dec 2025). Check hksquash.org.hk for official announcement.</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>28 Dec 2026</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>30 Dec 2026</t>
         </is>
       </c>
-      <c r="C55" s="11" t="inlineStr">
+      <c r="C57" s="11" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>Scottish Junior Open 2026</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E57" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F55" s="11" t="inlineStr">
+      <c r="F57" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G55" s="11" t="inlineStr"/>
-      <c r="H55" s="12" t="inlineStr">
+      <c r="G57" s="11" t="inlineStr"/>
+      <c r="H57" s="12" t="inlineStr">
         <is>
           <t>ESF / Scottish Squash</t>
         </is>
       </c>
-      <c r="I55" s="12" t="inlineStr">
+      <c r="I57" s="12" t="inlineStr">
         <is>
           <t>Oriam &amp; Edinburgh Sports Club, Edinburgh</t>
         </is>
       </c>
-      <c r="J55" s="12" t="inlineStr">
+      <c r="J57" s="12" t="inlineStr">
         <is>
           <t>Scotland</t>
         </is>
       </c>
-      <c r="K55" s="12" t="inlineStr">
+      <c r="K57" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L55" s="12" t="inlineStr">
+      <c r="L57" s="12" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Silver. Lead-in event to British Junior Open 2027. Source: scottishsquash.org / europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>2 Jan 2027</t>
         </is>
       </c>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="B58" s="9" t="inlineStr">
         <is>
           <t>6 Jan 2027</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D56" s="10" t="inlineStr">
+      <c r="D58" s="10" t="inlineStr">
         <is>
           <t>British Junior Open 2027</t>
         </is>
       </c>
-      <c r="E56" s="10" t="inlineStr">
+      <c r="E58" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="F56" s="9" t="inlineStr">
+      <c r="F58" s="9" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr"/>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="G58" s="9" t="inlineStr"/>
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>England Squash / BJO</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>Birmingham, England</t>
         </is>
       </c>
-      <c r="J56" s="10" t="inlineStr">
+      <c r="J58" s="10" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="K56" s="10" t="inlineStr">
+      <c r="K58" s="10" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L56" s="10" t="inlineStr">
+      <c r="L58" s="10" t="inlineStr">
         <is>
           <t>Officially confirmed 2-6 Jan 2027. 750+ players from 50+ countries. Source: britishjunioropen.com/save-the-dates-british-junior-open-2027</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
         <is>
           <t>14 Jan 2027</t>
         </is>
       </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>17 Jan 2027</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D57" s="8" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>Czech Junior Open 2027</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G57" s="7" t="inlineStr"/>
-      <c r="H57" s="8" t="inlineStr">
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="8" t="inlineStr">
         <is>
           <t>ESF / Czech Squash Federation</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
+      <c r="I59" s="8" t="inlineStr">
         <is>
           <t>Prague, Czech Republic</t>
         </is>
       </c>
-      <c r="J57" s="8" t="inlineStr">
+      <c r="J59" s="8" t="inlineStr">
         <is>
           <t>Czech Republic</t>
         </is>
       </c>
-      <c r="K57" s="8" t="inlineStr">
+      <c r="K59" s="8" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L57" s="8" t="inlineStr">
+      <c r="L59" s="8" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Gold. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>16 Jan 2027</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>18 Jan 2027</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>US Connecticut JCT 2027</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E60" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F60" s="5" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr"/>
-      <c r="H58" s="6" t="inlineStr">
+      <c r="G60" s="5" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr">
         <is>
           <t>US Squash</t>
         </is>
       </c>
-      <c r="I58" s="6" t="inlineStr">
+      <c r="I60" s="6" t="inlineStr">
         <is>
           <t>Stamford / Norwalk, CT</t>
         </is>
       </c>
-      <c r="J58" s="6" t="inlineStr">
+      <c r="J60" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K58" s="6" t="inlineStr">
+      <c r="K60" s="6" t="inlineStr">
         <is>
           <t>All junior age groups</t>
         </is>
       </c>
-      <c r="L58" s="6" t="inlineStr">
+      <c r="L60" s="6" t="inlineStr">
         <is>
           <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>29 Jan 2027</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>31 Jan 2027</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>Slovenia Junior Open 2027</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E61" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr">
+      <c r="F61" s="3" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="4" t="inlineStr">
         <is>
           <t>ESF / Squash Slovenia</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr">
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>Ljubljana, Slovenia</t>
         </is>
       </c>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="K59" s="4" t="inlineStr">
+      <c r="K61" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L59" s="4" t="inlineStr">
+      <c r="L61" s="4" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="11" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
         <is>
           <t>10 Feb 2027</t>
         </is>
       </c>
-      <c r="B60" s="11" t="inlineStr">
+      <c r="B62" s="11" t="inlineStr">
         <is>
           <t>14 Feb 2027</t>
         </is>
       </c>
-      <c r="C60" s="11" t="inlineStr">
+      <c r="C62" s="11" t="inlineStr">
         <is>
           <t>Wed</t>
         </is>
       </c>
-      <c r="D60" s="12" t="inlineStr">
+      <c r="D62" s="12" t="inlineStr">
         <is>
           <t>Sri Lanka Junior Squash Open 2027 ★</t>
         </is>
       </c>
-      <c r="E60" s="12" t="inlineStr">
+      <c r="E62" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F60" s="11" t="inlineStr">
+      <c r="F62" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G60" s="11" t="inlineStr"/>
-      <c r="H60" s="12" t="inlineStr">
+      <c r="G62" s="11" t="inlineStr"/>
+      <c r="H62" s="12" t="inlineStr">
         <is>
           <t>Sri Lanka Squash / ASF</t>
         </is>
       </c>
-      <c r="I60" s="12" t="inlineStr">
+      <c r="I62" s="12" t="inlineStr">
         <is>
           <t>Ratmalana, Sri Lanka</t>
         </is>
       </c>
-      <c r="J60" s="12" t="inlineStr">
+      <c r="J62" s="12" t="inlineStr">
         <is>
           <t>Sri Lanka</t>
         </is>
       </c>
-      <c r="K60" s="12" t="inlineStr">
+      <c r="K62" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L60" s="12" t="inlineStr">
+      <c r="L62" s="12" t="inlineStr">
         <is>
           <t>AJSS Silver. Entry deadline: 4 Jan 2027. Source: asiansquash.org/eventpage/ajss-event</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="11" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
         <is>
           <t>11 Feb 2027</t>
         </is>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B63" s="11" t="inlineStr">
         <is>
           <t>14 Feb 2027</t>
         </is>
       </c>
-      <c r="C61" s="11" t="inlineStr">
+      <c r="C63" s="11" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D61" s="12" t="inlineStr">
+      <c r="D63" s="12" t="inlineStr">
         <is>
           <t>Swiss Junior Open 2027</t>
         </is>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F61" s="11" t="inlineStr">
+      <c r="F63" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G61" s="11" t="inlineStr"/>
-      <c r="H61" s="12" t="inlineStr">
+      <c r="G63" s="11" t="inlineStr"/>
+      <c r="H63" s="12" t="inlineStr">
         <is>
           <t>ESF / Swiss Squash</t>
         </is>
       </c>
-      <c r="I61" s="12" t="inlineStr">
+      <c r="I63" s="12" t="inlineStr">
         <is>
           <t>Langnau am Albis, Switzerland</t>
         </is>
       </c>
-      <c r="J61" s="12" t="inlineStr">
+      <c r="J63" s="12" t="inlineStr">
         <is>
           <t>Switzerland</t>
         </is>
       </c>
-      <c r="K61" s="12" t="inlineStr">
+      <c r="K63" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L61" s="12" t="inlineStr">
+      <c r="L63" s="12" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Silver. Source: europeansquash.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>13 Feb 2027</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>15 Feb 2027</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Sat</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>US Texas JCT 2027</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>National/Regional</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G62" s="5" t="inlineStr"/>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>US Squash</t>
-        </is>
-      </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>Houston, TX</t>
-        </is>
-      </c>
-      <c r="J62" s="6" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="K62" s="6" t="inlineStr">
-        <is>
-          <t>All junior age groups</t>
-        </is>
-      </c>
-      <c r="L62" s="6" t="inlineStr">
-        <is>
-          <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>18 Feb 2027</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>21 Feb 2027</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>Thu</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>German Junior Open 2027</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr"/>
-      <c r="H63" s="8" t="inlineStr">
-        <is>
-          <t>ESF / German Squash Federation</t>
-        </is>
-      </c>
-      <c r="I63" s="8" t="inlineStr">
-        <is>
-          <t>Hamburg, Germany</t>
-        </is>
-      </c>
-      <c r="J63" s="8" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="K63" s="8" t="inlineStr">
-        <is>
-          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
-        </is>
-      </c>
-      <c r="L63" s="8" t="inlineStr">
-        <is>
-          <t>ESF Junior Circuit Gold. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>19 Feb 2027</t>
+          <t>13 Feb 2027</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>21 Feb 2027</t>
+          <t>15 Feb 2027</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Fri</t>
+          <t>Sat</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>US High School Championships 2027</t>
+          <t>US Texas JCT 2027</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -24355,266 +24355,266 @@
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
+          <t>Houston, TX</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>All junior age groups</t>
+        </is>
+      </c>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>US Squash Junior Championship Tour. Source: ussquash.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>18 Feb 2027</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>21 Feb 2027</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>German Junior Open 2027</t>
+        </is>
+      </c>
+      <c r="E65" s="8" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr"/>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>ESF / German Squash Federation</t>
+        </is>
+      </c>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>Hamburg, Germany</t>
+        </is>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L65" s="8" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Gold. Source: europeansquash.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>19 Feb 2027</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>21 Feb 2027</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>US High School Championships 2027</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>National/Regional</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr"/>
+      <c r="H66" s="6" t="inlineStr">
+        <is>
+          <t>US Squash</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
           <t>Philadelphia, PA</t>
         </is>
       </c>
-      <c r="J64" s="6" t="inlineStr">
+      <c r="J66" s="6" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="K64" s="6" t="inlineStr">
+      <c r="K66" s="6" t="inlineStr">
         <is>
           <t>High School age groups</t>
         </is>
       </c>
-      <c r="L64" s="6" t="inlineStr">
+      <c r="L66" s="6" t="inlineStr">
         <is>
           <t>US national high school squash championships. Source: ussquash.org</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="23" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="23" t="inlineStr">
         <is>
           <t>23 Feb 2027</t>
         </is>
       </c>
-      <c r="B65" s="23" t="inlineStr">
+      <c r="B67" s="23" t="inlineStr">
         <is>
           <t>27 Feb 2027</t>
         </is>
       </c>
-      <c r="C65" s="23" t="inlineStr">
+      <c r="C67" s="23" t="inlineStr">
         <is>
           <t>Tue</t>
         </is>
       </c>
-      <c r="D65" s="24" t="inlineStr">
+      <c r="D67" s="24" t="inlineStr">
         <is>
           <t>23rd Asian Junior Team Championships 2027</t>
         </is>
       </c>
-      <c r="E65" s="24" t="inlineStr">
+      <c r="E67" s="24" t="inlineStr">
         <is>
           <t>Asian Championship</t>
         </is>
       </c>
-      <c r="F65" s="23" t="inlineStr">
+      <c r="F67" s="23" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G65" s="23" t="inlineStr"/>
-      <c r="H65" s="24" t="inlineStr">
+      <c r="G67" s="23" t="inlineStr"/>
+      <c r="H67" s="24" t="inlineStr">
         <is>
           <t>Asian Squash Federation (ASF)</t>
         </is>
       </c>
-      <c r="I65" s="24" t="inlineStr">
+      <c r="I67" s="24" t="inlineStr">
         <is>
           <t>Thailand (venue TBC)</t>
         </is>
       </c>
-      <c r="J65" s="24" t="inlineStr">
+      <c r="J67" s="24" t="inlineStr">
         <is>
           <t>Thailand</t>
         </is>
       </c>
-      <c r="K65" s="24" t="inlineStr">
+      <c r="K67" s="24" t="inlineStr">
         <is>
           <t>U19 (B&amp;G — team format)</t>
         </is>
       </c>
-      <c r="L65" s="24" t="inlineStr">
+      <c r="L67" s="24" t="inlineStr">
         <is>
           <t>Confirmed on ASF 2026-27 calendar. Exact venue TBC. Source: asiansquash.org + thesquashsite.com</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="11" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>26 Feb 2027</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B68" s="11" t="inlineStr">
         <is>
           <t>28 Feb 2027</t>
         </is>
       </c>
-      <c r="C66" s="11" t="inlineStr">
+      <c r="C68" s="11" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>Austrian Junior Open 2027</t>
         </is>
       </c>
-      <c r="E66" s="12" t="inlineStr">
+      <c r="E68" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F66" s="11" t="inlineStr">
+      <c r="F68" s="11" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G66" s="11" t="inlineStr"/>
-      <c r="H66" s="12" t="inlineStr">
+      <c r="G68" s="11" t="inlineStr"/>
+      <c r="H68" s="12" t="inlineStr">
         <is>
           <t>ESF / Austrian Squash Federation</t>
         </is>
       </c>
-      <c r="I66" s="12" t="inlineStr">
+      <c r="I68" s="12" t="inlineStr">
         <is>
           <t>Vienna, Austria</t>
         </is>
       </c>
-      <c r="J66" s="12" t="inlineStr">
+      <c r="J68" s="12" t="inlineStr">
         <is>
           <t>Austria</t>
         </is>
       </c>
-      <c r="K66" s="12" t="inlineStr">
+      <c r="K68" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L66" s="12" t="inlineStr">
+      <c r="L68" s="12" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Silver. Source: europeansquash.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>12 Mar 2027</t>
-        </is>
-      </c>
-      <c r="B67" s="5" t="inlineStr">
-        <is>
-          <t>14 Mar 2027</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>US Junior Squash Championships 2027</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>National/Regional</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G67" s="5" t="inlineStr"/>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>US Squash</t>
-        </is>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA</t>
-        </is>
-      </c>
-      <c r="J67" s="6" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="K67" s="6" t="inlineStr">
-        <is>
-          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
-        </is>
-      </c>
-      <c r="L67" s="6" t="inlineStr">
-        <is>
-          <t>US national junior championships. Source: ussquash.org</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>12 Mar 2027</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>14 Mar 2027</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>Fri</t>
-        </is>
-      </c>
-      <c r="D68" s="4" t="inlineStr">
-        <is>
-          <t>Croatian Junior Open 2027</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>✓ Confirmed</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr"/>
-      <c r="H68" s="4" t="inlineStr">
-        <is>
-          <t>ESF / Croatian Squash Federation</t>
-        </is>
-      </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>Zagreb, Croatia</t>
-        </is>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
-      </c>
-      <c r="K68" s="4" t="inlineStr">
-        <is>
-          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
-        </is>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>ESF Junior Circuit Bronze. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>19 Mar 2027</t>
+          <t>12 Mar 2027</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>21 Mar 2027</t>
+          <t>14 Mar 2027</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
@@ -24624,7 +24624,7 @@
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>US Junior Divisional Championships 2027</t>
+          <t>US Junior Squash Championships 2027</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -24645,7 +24645,7 @@
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>USA (venue TBC)</t>
+          <t>Philadelphia, PA</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
@@ -24655,24 +24655,24 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>All junior age groups</t>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr">
         <is>
-          <t>US Squash regional divisional event. Source: ussquash.org</t>
+          <t>US national junior championships. Source: ussquash.org</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>19 Mar 2027</t>
+          <t>12 Mar 2027</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>21 Mar 2027</t>
+          <t>14 Mar 2027</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -24682,7 +24682,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Norwegian Junior Open 2027</t>
+          <t>Croatian Junior Open 2027</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -24698,274 +24698,390 @@
       <c r="G70" s="3" t="inlineStr"/>
       <c r="H70" s="4" t="inlineStr">
         <is>
+          <t>ESF / Croatian Squash Federation</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>Zagreb, Croatia</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Bronze. Source: europeansquash.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>19 Mar 2027</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>21 Mar 2027</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>US Junior Divisional Championships 2027</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>National/Regional</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G71" s="5" t="inlineStr"/>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
+          <t>US Squash</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>USA (venue TBC)</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>All junior age groups</t>
+        </is>
+      </c>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>US Squash regional divisional event. Source: ussquash.org</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>19 Mar 2027</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>21 Mar 2027</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Norwegian Junior Open 2027</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
           <t>ESF / Squash Norway</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr">
+      <c r="I72" s="4" t="inlineStr">
         <is>
           <t>Lysaker, Norway</t>
         </is>
       </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="J72" s="4" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="K70" s="4" t="inlineStr">
+      <c r="K72" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L70" s="4" t="inlineStr">
+      <c r="L72" s="4" t="inlineStr">
         <is>
           <t>ESF Junior Circuit Bronze. Source: europeansquash.com</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="27" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="27" t="inlineStr">
         <is>
           <t>27 Mar 2027</t>
         </is>
       </c>
-      <c r="B71" s="27" t="inlineStr">
+      <c r="B73" s="27" t="inlineStr">
         <is>
           <t>4 Apr 2027</t>
         </is>
       </c>
-      <c r="C71" s="27" t="inlineStr">
+      <c r="C73" s="27" t="inlineStr">
         <is>
           <t>Sat</t>
         </is>
       </c>
-      <c r="D71" s="28" t="inlineStr">
+      <c r="D73" s="28" t="inlineStr">
         <is>
           <t>PSA World Championships 2026-27</t>
         </is>
       </c>
-      <c r="E71" s="28" t="inlineStr">
+      <c r="E73" s="28" t="inlineStr">
         <is>
           <t>World Championship</t>
         </is>
       </c>
-      <c r="F71" s="27" t="inlineStr">
+      <c r="F73" s="27" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G71" s="27" t="inlineStr"/>
-      <c r="H71" s="28" t="inlineStr">
+      <c r="G73" s="27" t="inlineStr"/>
+      <c r="H73" s="28" t="inlineStr">
         <is>
           <t>PSA World Tour / England Squash</t>
         </is>
       </c>
-      <c r="I71" s="28" t="inlineStr">
+      <c r="I73" s="28" t="inlineStr">
         <is>
           <t>London, England</t>
         </is>
       </c>
-      <c r="J71" s="28" t="inlineStr">
+      <c r="J73" s="28" t="inlineStr">
         <is>
           <t>England</t>
         </is>
       </c>
-      <c r="K71" s="28" t="inlineStr">
+      <c r="K73" s="28" t="inlineStr">
         <is>
           <t>Open (professional)</t>
         </is>
       </c>
-      <c r="L71" s="28" t="inlineStr">
+      <c r="L73" s="28" t="inlineStr">
         <is>
           <t>Professional event — included for reference. Source: worldsquashchamps.com</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="27" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="27" t="inlineStr">
         <is>
           <t>7 Jun 2027</t>
         </is>
       </c>
-      <c r="B72" s="27" t="inlineStr">
+      <c r="B74" s="27" t="inlineStr">
         <is>
           <t>13 Jun 2027</t>
         </is>
       </c>
-      <c r="C72" s="27" t="inlineStr">
+      <c r="C74" s="27" t="inlineStr">
         <is>
           <t>Mon</t>
         </is>
       </c>
-      <c r="D72" s="28" t="inlineStr">
+      <c r="D74" s="28" t="inlineStr">
         <is>
           <t>WSF World Under-23 Championships 2027</t>
         </is>
       </c>
-      <c r="E72" s="28" t="inlineStr">
+      <c r="E74" s="28" t="inlineStr">
         <is>
           <t>World Championship</t>
         </is>
       </c>
-      <c r="F72" s="27" t="inlineStr">
+      <c r="F74" s="27" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>
       </c>
-      <c r="G72" s="27" t="inlineStr"/>
-      <c r="H72" s="28" t="inlineStr">
+      <c r="G74" s="27" t="inlineStr"/>
+      <c r="H74" s="28" t="inlineStr">
         <is>
           <t>World Squash Federation (WSF)</t>
         </is>
       </c>
-      <c r="I72" s="28" t="inlineStr">
+      <c r="I74" s="28" t="inlineStr">
         <is>
           <t>Karachi, Pakistan</t>
         </is>
       </c>
-      <c r="J72" s="28" t="inlineStr">
+      <c r="J74" s="28" t="inlineStr">
         <is>
           <t>Pakistan</t>
         </is>
       </c>
-      <c r="K72" s="28" t="inlineStr">
+      <c r="K74" s="28" t="inlineStr">
         <is>
           <t>U23 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L72" s="28" t="inlineStr">
+      <c r="L74" s="28" t="inlineStr">
         <is>
           <t>WSF global event for under-23 players. Source: worldsquash.sport</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="31" t="inlineStr">
         <is>
           <t>COLOUR KEY — AJSS Levels: Diamond &gt; Platinum &gt; Gold &gt; Silver &gt; Bronze</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="28" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>World Championship</t>
         </is>
       </c>
-      <c r="B75" s="28" t="inlineStr">
+      <c r="B77" s="28" t="inlineStr">
         <is>
           <t>WSF / PSA global championship — pinnacle events</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="24" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="24" t="inlineStr">
         <is>
           <t>Asian Championship</t>
         </is>
       </c>
-      <c r="B76" s="24" t="inlineStr">
+      <c r="B78" s="24" t="inlineStr">
         <is>
           <t>ASF continental championships (Asian Junior Individual &amp; Team)</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="30" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="30" t="inlineStr">
         <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="B77" s="30" t="inlineStr">
+      <c r="B79" s="30" t="inlineStr">
         <is>
           <t>AJSS Diamond — highest AJSS tier (e.g. Milo Malaysia)</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="10" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>Platinum</t>
         </is>
       </c>
-      <c r="B78" s="10" t="inlineStr">
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>AJSS Platinum / ESF Platinum — highest open tier (HK Junior, BJO, Singapore JO, KL JO, Indian JO)</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>AJSS Gold / ESF Gold — second tier (Korea, Japan, Penang, Lion City, Slams, Dutch JO, German JO)</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="12" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="B80" s="12" t="inlineStr">
+      <c r="B82" s="12" t="inlineStr">
         <is>
           <t>AJSS Silver / ESF Silver — third tier (Sri Lanka, Australia, China, Qatar, Chinese Taipei, Swiss JO)</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B83" s="4" t="inlineStr">
         <is>
           <t>ESF Bronze — fourth tier European circuit (Slovenia, Croatia, Norway)</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>National/Regional</t>
         </is>
       </c>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>National tour stops and domestic championships (US Squash JCT / High School / Divisional)</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="26" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="26" t="inlineStr">
         <is>
           <t>~ Estimated</t>
         </is>
       </c>
-      <c r="B83" s="26" t="inlineStr">
+      <c r="B85" s="26" t="inlineStr">
         <is>
           <t>AMBER = dates not yet officially confirmed — verify with the relevant federation before travel/planning</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:L72"/>
+  <autoFilter ref="A2:L74"/>
   <mergeCells count="11">
     <mergeCell ref="B83:L83"/>
-    <mergeCell ref="B75:L75"/>
+    <mergeCell ref="A76:L76"/>
     <mergeCell ref="B82:L82"/>
     <mergeCell ref="B78:L78"/>
     <mergeCell ref="B77:L77"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="B80:L80"/>
     <mergeCell ref="B81:L81"/>
-    <mergeCell ref="A74:L74"/>
-    <mergeCell ref="B76:L76"/>
+    <mergeCell ref="B85:L85"/>
+    <mergeCell ref="B84:L84"/>
     <mergeCell ref="B79:L79"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Holiday_Calendar_2026_2027.xlsx
+++ b/Holiday_Calendar_2026_2027.xlsx
@@ -23389,60 +23389,60 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="25" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>5 Nov 2026</t>
         </is>
       </c>
-      <c r="B48" s="25" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>8 Nov 2026</t>
         </is>
       </c>
-      <c r="C48" s="25" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Thu</t>
         </is>
       </c>
-      <c r="D48" s="26" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>Polish Junior Open 2026</t>
         </is>
       </c>
-      <c r="E48" s="26" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F48" s="25" t="inlineStr">
-        <is>
-          <t>~ Estimated</t>
-        </is>
-      </c>
-      <c r="G48" s="25" t="inlineStr"/>
-      <c r="H48" s="26" t="inlineStr">
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>ESF / Polish Squash Federation</t>
         </is>
       </c>
-      <c r="I48" s="26" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>Kraków, Poland</t>
         </is>
       </c>
-      <c r="J48" s="26" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr">
         <is>
           <t>Poland</t>
         </is>
       </c>
-      <c r="K48" s="26" t="inlineStr">
+      <c r="K48" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L48" s="26" t="inlineStr">
-        <is>
-          <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/polish-junior-open-2026</t>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Bronze. Entry deadline: 16 Oct 2026. Source: europeansquash.com/event/polish-junior-open-2026</t>
         </is>
       </c>
     </row>
@@ -23855,17 +23855,17 @@
     <row r="56">
       <c r="A56" s="25" t="inlineStr">
         <is>
-          <t>20 Dec 2026</t>
+          <t>24 Dec 2026</t>
         </is>
       </c>
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>26 Dec 2026</t>
+          <t>29 Dec 2026</t>
         </is>
       </c>
       <c r="C56" s="25" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Thu</t>
         </is>
       </c>
       <c r="D56" s="26" t="inlineStr">
@@ -23906,7 +23906,7 @@
       </c>
       <c r="L56" s="26" t="inlineStr">
         <is>
-          <t>AJSS Platinum. NOT YET listed on ASF page — dates estimated from prior years (2025 edition: 19-24 Dec 2025). Check hksquash.org.hk for official announcement.</t>
+          <t>AJSS Platinum. Verbally confirmed 24-29 Dec 2026. Official announcement pending on hksquash.org.hk.</t>
         </is>
       </c>
     </row>

--- a/Holiday_Calendar_2026_2027.xlsx
+++ b/Holiday_Calendar_2026_2027.xlsx
@@ -22863,60 +22863,60 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="25" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>9 Oct 2026</t>
         </is>
       </c>
-      <c r="B39" s="25" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>11 Oct 2026</t>
         </is>
       </c>
-      <c r="C39" s="25" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D39" s="26" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>Hungarian Junior Open 2026</t>
         </is>
       </c>
-      <c r="E39" s="26" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F39" s="25" t="inlineStr">
-        <is>
-          <t>~ Estimated</t>
-        </is>
-      </c>
-      <c r="G39" s="25" t="inlineStr"/>
-      <c r="H39" s="26" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>ESF / Hungarian Squash Federation</t>
         </is>
       </c>
-      <c r="I39" s="26" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>Budapest, Hungary</t>
         </is>
       </c>
-      <c r="J39" s="26" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>Hungary</t>
         </is>
       </c>
-      <c r="K39" s="26" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L39" s="26" t="inlineStr">
-        <is>
-          <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/hungarian-junior-open-2026</t>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Bronze. Event concluded as scheduled (City Squash Club) — results reported on squash.hu. Source: europeansquash.com/event/hungarian-junior-open-2026</t>
         </is>
       </c>
     </row>
@@ -23037,60 +23037,60 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="25" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>16 Oct 2026</t>
         </is>
       </c>
-      <c r="B42" s="25" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>18 Oct 2026</t>
         </is>
       </c>
-      <c r="C42" s="25" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D42" s="26" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>Romanian Junior Open 2026</t>
         </is>
       </c>
-      <c r="E42" s="26" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F42" s="25" t="inlineStr">
-        <is>
-          <t>~ Estimated</t>
-        </is>
-      </c>
-      <c r="G42" s="25" t="inlineStr"/>
-      <c r="H42" s="26" t="inlineStr">
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>ESF / Romanian Squash Federation</t>
         </is>
       </c>
-      <c r="I42" s="26" t="inlineStr">
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>Bucharest, Romania</t>
         </is>
       </c>
-      <c r="J42" s="26" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>Romania</t>
         </is>
       </c>
-      <c r="K42" s="26" t="inlineStr">
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L42" s="26" t="inlineStr">
-        <is>
-          <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/romanian-junior-open-2026</t>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Bronze. Confirmed on ESF events calendar. Source: europeansquash.com/event/romanian-junior-open-2026</t>
         </is>
       </c>
     </row>
@@ -23153,60 +23153,60 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="25" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
       </c>
-      <c r="B44" s="25" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>25 Oct 2026</t>
         </is>
       </c>
-      <c r="C44" s="25" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D44" s="26" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>Lithuanian Junior Open 2026</t>
         </is>
       </c>
-      <c r="E44" s="26" t="inlineStr">
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="F44" s="25" t="inlineStr">
-        <is>
-          <t>~ Estimated</t>
-        </is>
-      </c>
-      <c r="G44" s="25" t="inlineStr"/>
-      <c r="H44" s="26" t="inlineStr">
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>ESF / Lithuanian Squash Federation</t>
         </is>
       </c>
-      <c r="I44" s="26" t="inlineStr">
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>Kaunas, Lithuania</t>
         </is>
       </c>
-      <c r="J44" s="26" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr">
         <is>
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="K44" s="26" t="inlineStr">
+      <c r="K44" s="4" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L44" s="26" t="inlineStr">
-        <is>
-          <t>ESF Junior Circuit Bronze. Source: europeansquash.com/event/lithuanian-junior-open-2026</t>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Bronze. Confirmed on ESF events calendar. Source: europeansquash.com/event/lithuanian-junior-open-2026</t>
         </is>
       </c>
     </row>
@@ -23505,60 +23505,60 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="25" t="inlineStr">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>13 Nov 2026</t>
         </is>
       </c>
-      <c r="B50" s="25" t="inlineStr">
+      <c r="B50" s="11" t="inlineStr">
         <is>
           <t>15 Nov 2026</t>
         </is>
       </c>
-      <c r="C50" s="25" t="inlineStr">
+      <c r="C50" s="11" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="D50" s="26" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>Irish Junior Open 2026</t>
         </is>
       </c>
-      <c r="E50" s="26" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr">
         <is>
           <t>Silver</t>
         </is>
       </c>
-      <c r="F50" s="25" t="inlineStr">
-        <is>
-          <t>~ Estimated</t>
-        </is>
-      </c>
-      <c r="G50" s="25" t="inlineStr"/>
-      <c r="H50" s="26" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr"/>
+      <c r="H50" s="12" t="inlineStr">
         <is>
           <t>ESF / Squash Ireland</t>
         </is>
       </c>
-      <c r="I50" s="26" t="inlineStr">
+      <c r="I50" s="12" t="inlineStr">
         <is>
           <t>Dublin, Ireland</t>
         </is>
       </c>
-      <c r="J50" s="26" t="inlineStr">
+      <c r="J50" s="12" t="inlineStr">
         <is>
           <t>Ireland</t>
         </is>
       </c>
-      <c r="K50" s="26" t="inlineStr">
+      <c r="K50" s="12" t="inlineStr">
         <is>
           <t>U11/U13/U15/U17/U19 (B&amp;G)</t>
         </is>
       </c>
-      <c r="L50" s="26" t="inlineStr">
-        <is>
-          <t>ESF Junior Circuit Silver. Source: europeansquash.com/event/irish-junior-open-2026</t>
+      <c r="L50" s="12" t="inlineStr">
+        <is>
+          <t>ESF Junior Circuit Silver. Confirmed on ESF events calendar, 13-15 Nov Dublin (Sutton LTC &amp; ALSAA). Entry deadline 30 Oct, 162 players last year. Source: europeansquash.com/event/irish-junior-open-2026</t>
         </is>
       </c>
     </row>
